--- a/doc/notes/ro-rl78-maxv-learning.xlsx
+++ b/doc/notes/ro-rl78-maxv-learning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\0_forge\ro-rl78-maxv-learning\doc\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534CA13F-4A29-4CD9-AECD-8CD6527FAE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845FE8D0-A19B-4EF7-AF4D-F3D9E9B2953E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9360" yWindow="8070" windowWidth="31455" windowHeight="20730" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="SVF" sheetId="23" r:id="rId16"/>
     <sheet name="ROM" sheetId="25" r:id="rId17"/>
     <sheet name="FLOW" sheetId="26" r:id="rId18"/>
+    <sheet name="DMA" sheetId="27" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4'!$A$6:$AB$70</definedName>
@@ -40,7 +41,6 @@
     <definedName name="PT">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="750">
   <si>
     <t>Block Diagram</t>
   </si>
@@ -2443,6 +2443,430 @@
   <si>
     <t>SIR &lt;count&gt; TDI (value) TDO (value) MASK (value);</t>
   </si>
+  <si>
+    <r>
+      <t>#define</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> DMA_START(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFA657"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>adr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFA657"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>cnt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD7BA7D"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>\</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC586C0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>do</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD7BA7D"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>\</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">{ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD7BA7D"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>\</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        DRC0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0x80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD7BA7D"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>\</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD2A8FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(); </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD7BA7D"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>\</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        DRA0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7B72"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>uint16_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">)adr; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD7BA7D"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>\</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        DBC0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> cnt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD7BA7D"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>\</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        DST0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC9D1D9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD7BA7D"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>\</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>    }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC586C0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>while</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8B949E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> // Wait for DMA0 to complete. UART reception continues during this loop. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#define</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> DMA_WAIT() </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD7BA7D"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>\</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC586C0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>while</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(DST0)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -2451,7 +2875,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2590,6 +3014,66 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC586C0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF569CD6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFA657"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD7BA7D"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC9D1D9"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFB5CEA8"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD2A8FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF7B72"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF8B949E"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="11">
@@ -3611,7 +4095,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3892,144 +4376,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="53" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="24" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="25" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="67" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="17" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="68" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="16" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4063,19 +4409,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="4" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4107,35 +4441,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4155,45 +4462,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4220,8 +4505,167 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="25" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="24" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="67" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="17" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="68" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="16" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="53" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -23846,11 +24290,11 @@
       <c r="H4" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="J4" s="198" t="s">
+      <c r="J4" s="165" t="s">
         <v>664</v>
       </c>
-      <c r="K4" s="198"/>
-      <c r="L4" s="198"/>
+      <c r="K4" s="165"/>
+      <c r="L4" s="165"/>
     </row>
     <row r="5" spans="2:12">
       <c r="B5" s="14">
@@ -26226,32 +26670,32 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:20">
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118" t="s">
+      <c r="B4" s="169"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169" t="s">
         <v>442</v>
       </c>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="169"/>
+      <c r="I4" s="169"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="169"/>
+      <c r="P4" s="169"/>
+      <c r="Q4" s="169"/>
+      <c r="R4" s="169"/>
+      <c r="S4" s="169"/>
+      <c r="T4" s="169"/>
     </row>
     <row r="5" spans="2:20">
-      <c r="B5" s="118"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="44">
         <v>0</v>
       </c>
@@ -26302,9 +26746,9 @@
       </c>
     </row>
     <row r="6" spans="2:20" ht="103.5" customHeight="1">
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
+      <c r="B6" s="169"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
       <c r="E6" s="63" t="s">
         <v>440</v>
       </c>
@@ -26355,7 +26799,7 @@
       </c>
     </row>
     <row r="7" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B7" s="115" t="s">
+      <c r="B7" s="166" t="s">
         <v>441</v>
       </c>
       <c r="C7" s="44">
@@ -26414,7 +26858,7 @@
       </c>
     </row>
     <row r="8" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B8" s="116"/>
+      <c r="B8" s="167"/>
       <c r="C8" s="44">
         <v>1</v>
       </c>
@@ -26471,7 +26915,7 @@
       </c>
     </row>
     <row r="9" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B9" s="116"/>
+      <c r="B9" s="167"/>
       <c r="C9" s="44">
         <v>2</v>
       </c>
@@ -26528,7 +26972,7 @@
       </c>
     </row>
     <row r="10" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B10" s="116"/>
+      <c r="B10" s="167"/>
       <c r="C10" s="44">
         <v>3</v>
       </c>
@@ -26585,7 +27029,7 @@
       </c>
     </row>
     <row r="11" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B11" s="116"/>
+      <c r="B11" s="167"/>
       <c r="C11" s="44">
         <v>4</v>
       </c>
@@ -26642,7 +27086,7 @@
       </c>
     </row>
     <row r="12" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B12" s="116"/>
+      <c r="B12" s="167"/>
       <c r="C12" s="44">
         <v>5</v>
       </c>
@@ -26699,7 +27143,7 @@
       </c>
     </row>
     <row r="13" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B13" s="116"/>
+      <c r="B13" s="167"/>
       <c r="C13" s="44">
         <v>6</v>
       </c>
@@ -26756,7 +27200,7 @@
       </c>
     </row>
     <row r="14" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B14" s="116"/>
+      <c r="B14" s="167"/>
       <c r="C14" s="44">
         <v>7</v>
       </c>
@@ -26813,7 +27257,7 @@
       </c>
     </row>
     <row r="15" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B15" s="116"/>
+      <c r="B15" s="167"/>
       <c r="C15" s="44">
         <v>8</v>
       </c>
@@ -26870,7 +27314,7 @@
       </c>
     </row>
     <row r="16" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B16" s="116"/>
+      <c r="B16" s="167"/>
       <c r="C16" s="44">
         <v>9</v>
       </c>
@@ -26927,7 +27371,7 @@
       </c>
     </row>
     <row r="17" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B17" s="116"/>
+      <c r="B17" s="167"/>
       <c r="C17" s="44">
         <v>10</v>
       </c>
@@ -26984,7 +27428,7 @@
       </c>
     </row>
     <row r="18" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B18" s="116"/>
+      <c r="B18" s="167"/>
       <c r="C18" s="44">
         <v>11</v>
       </c>
@@ -27041,7 +27485,7 @@
       </c>
     </row>
     <row r="19" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B19" s="116"/>
+      <c r="B19" s="167"/>
       <c r="C19" s="44">
         <v>12</v>
       </c>
@@ -27098,7 +27542,7 @@
       </c>
     </row>
     <row r="20" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B20" s="116"/>
+      <c r="B20" s="167"/>
       <c r="C20" s="44">
         <v>13</v>
       </c>
@@ -27155,7 +27599,7 @@
       </c>
     </row>
     <row r="21" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B21" s="116"/>
+      <c r="B21" s="167"/>
       <c r="C21" s="44">
         <v>14</v>
       </c>
@@ -27214,7 +27658,7 @@
       <c r="V21" s="39"/>
     </row>
     <row r="22" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B22" s="117"/>
+      <c r="B22" s="168"/>
       <c r="C22" s="44">
         <v>15</v>
       </c>
@@ -30243,34 +30687,34 @@
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="142" t="s">
+      <c r="B3" s="191" t="s">
         <v>489</v>
       </c>
-      <c r="C3" s="137" t="s">
+      <c r="C3" s="204" t="s">
         <v>488</v>
       </c>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="134" t="s">
+      <c r="D3" s="202"/>
+      <c r="E3" s="202"/>
+      <c r="F3" s="202"/>
+      <c r="G3" s="202"/>
+      <c r="H3" s="205"/>
+      <c r="I3" s="201" t="s">
         <v>487</v>
       </c>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="135"/>
-      <c r="M3" s="135"/>
-      <c r="N3" s="136"/>
+      <c r="J3" s="202"/>
+      <c r="K3" s="202"/>
+      <c r="L3" s="202"/>
+      <c r="M3" s="202"/>
+      <c r="N3" s="203"/>
       <c r="O3" s="104" t="s">
         <v>486</v>
       </c>
-      <c r="P3" s="131" t="s">
+      <c r="P3" s="197" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B4" s="143"/>
+      <c r="B4" s="192"/>
       <c r="C4" s="105" t="s">
         <v>373</v>
       </c>
@@ -30310,7 +30754,7 @@
       <c r="O4" s="110" t="s">
         <v>479</v>
       </c>
-      <c r="P4" s="132"/>
+      <c r="P4" s="198"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickTop="1">
       <c r="B5" s="64" t="s">
@@ -30386,12 +30830,12 @@
         <f t="shared" si="0"/>
         <v>0x01</v>
       </c>
-      <c r="J6" s="122" t="s">
+      <c r="J6" s="199" t="s">
         <v>508</v>
       </c>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
+      <c r="K6" s="199"/>
+      <c r="L6" s="199"/>
+      <c r="M6" s="199"/>
       <c r="N6" s="77" t="s">
         <v>492</v>
       </c>
@@ -30428,12 +30872,12 @@
         <f t="shared" si="0"/>
         <v>0x02</v>
       </c>
-      <c r="J7" s="122" t="s">
+      <c r="J7" s="199" t="s">
         <v>523</v>
       </c>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
+      <c r="K7" s="199"/>
+      <c r="L7" s="199"/>
+      <c r="M7" s="199"/>
       <c r="N7" s="77" t="s">
         <v>492</v>
       </c>
@@ -30470,12 +30914,12 @@
         <f t="shared" si="0"/>
         <v>0x03</v>
       </c>
-      <c r="J8" s="122" t="s">
+      <c r="J8" s="199" t="s">
         <v>506</v>
       </c>
-      <c r="K8" s="122"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="122"/>
+      <c r="K8" s="199"/>
+      <c r="L8" s="199"/>
+      <c r="M8" s="199"/>
       <c r="N8" s="77" t="s">
         <v>492</v>
       </c>
@@ -30512,14 +30956,14 @@
         <f t="shared" si="0"/>
         <v>0x04</v>
       </c>
-      <c r="J9" s="122" t="s">
+      <c r="J9" s="199" t="s">
         <v>503</v>
       </c>
-      <c r="K9" s="122"/>
-      <c r="L9" s="122" t="s">
+      <c r="K9" s="199"/>
+      <c r="L9" s="199" t="s">
         <v>502</v>
       </c>
-      <c r="M9" s="122"/>
+      <c r="M9" s="199"/>
       <c r="N9" s="77" t="s">
         <v>492</v>
       </c>
@@ -30681,12 +31125,12 @@
       <c r="C13" s="73" t="s">
         <v>564</v>
       </c>
-      <c r="D13" s="133" t="s">
+      <c r="D13" s="200" t="s">
         <v>508</v>
       </c>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="200"/>
       <c r="H13" s="103" t="s">
         <v>492</v>
       </c>
@@ -30771,12 +31215,12 @@
       <c r="C15" s="73" t="s">
         <v>566</v>
       </c>
-      <c r="D15" s="122" t="s">
+      <c r="D15" s="199" t="s">
         <v>506</v>
       </c>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
+      <c r="E15" s="199"/>
+      <c r="F15" s="199"/>
+      <c r="G15" s="199"/>
       <c r="H15" s="75" t="s">
         <v>492</v>
       </c>
@@ -30813,14 +31257,14 @@
       <c r="C16" s="73" t="s">
         <v>567</v>
       </c>
-      <c r="D16" s="122" t="s">
+      <c r="D16" s="199" t="s">
         <v>503</v>
       </c>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122" t="s">
+      <c r="E16" s="199"/>
+      <c r="F16" s="199" t="s">
         <v>502</v>
       </c>
-      <c r="G16" s="122"/>
+      <c r="G16" s="199"/>
       <c r="H16" s="75" t="s">
         <v>492</v>
       </c>
@@ -31002,34 +31446,34 @@
       <c r="D21" s="58"/>
     </row>
     <row r="22" spans="2:16">
-      <c r="B22" s="144" t="s">
+      <c r="B22" s="193" t="s">
         <v>489</v>
       </c>
-      <c r="C22" s="153" t="s">
+      <c r="C22" s="176" t="s">
         <v>488</v>
       </c>
-      <c r="D22" s="154"/>
-      <c r="E22" s="154"/>
-      <c r="F22" s="154"/>
-      <c r="G22" s="154"/>
-      <c r="H22" s="154"/>
-      <c r="I22" s="154"/>
-      <c r="J22" s="155"/>
-      <c r="K22" s="153" t="s">
+      <c r="D22" s="177"/>
+      <c r="E22" s="177"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="177"/>
+      <c r="I22" s="177"/>
+      <c r="J22" s="178"/>
+      <c r="K22" s="176" t="s">
         <v>487</v>
       </c>
-      <c r="L22" s="154"/>
-      <c r="M22" s="154"/>
-      <c r="N22" s="155"/>
+      <c r="L22" s="177"/>
+      <c r="M22" s="177"/>
+      <c r="N22" s="178"/>
       <c r="O22" s="104" t="s">
         <v>486</v>
       </c>
-      <c r="P22" s="119" t="s">
+      <c r="P22" s="206" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B23" s="145"/>
+      <c r="B23" s="194"/>
       <c r="C23" s="111" t="s">
         <v>373</v>
       </c>
@@ -31045,21 +31489,21 @@
       <c r="G23" s="113" t="s">
         <v>482</v>
       </c>
-      <c r="H23" s="123" t="s">
+      <c r="H23" s="208" t="s">
         <v>481</v>
       </c>
-      <c r="I23" s="124"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="156" t="s">
+      <c r="I23" s="180"/>
+      <c r="J23" s="181"/>
+      <c r="K23" s="179" t="s">
         <v>480</v>
       </c>
-      <c r="L23" s="124"/>
-      <c r="M23" s="124"/>
-      <c r="N23" s="125"/>
+      <c r="L23" s="180"/>
+      <c r="M23" s="180"/>
+      <c r="N23" s="181"/>
       <c r="O23" s="110" t="s">
         <v>479</v>
       </c>
-      <c r="P23" s="120"/>
+      <c r="P23" s="207"/>
     </row>
     <row r="24" spans="2:16" ht="15.75" thickTop="1">
       <c r="B24" s="98" t="s">
@@ -31080,17 +31524,17 @@
       <c r="G24" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="H24" s="126" t="s">
+      <c r="H24" s="209" t="s">
         <v>571</v>
       </c>
-      <c r="I24" s="127"/>
-      <c r="J24" s="128"/>
-      <c r="K24" s="158" t="s">
+      <c r="I24" s="185"/>
+      <c r="J24" s="186"/>
+      <c r="K24" s="184" t="s">
         <v>571</v>
       </c>
-      <c r="L24" s="127"/>
-      <c r="M24" s="127"/>
-      <c r="N24" s="128"/>
+      <c r="L24" s="185"/>
+      <c r="M24" s="185"/>
+      <c r="N24" s="186"/>
       <c r="O24" s="55" t="s">
         <v>477</v>
       </c>
@@ -31117,17 +31561,17 @@
       <c r="G25" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="H25" s="121" t="s">
+      <c r="H25" s="190" t="s">
         <v>571</v>
       </c>
-      <c r="I25" s="129"/>
-      <c r="J25" s="130"/>
-      <c r="K25" s="148" t="s">
+      <c r="I25" s="188"/>
+      <c r="J25" s="189"/>
+      <c r="K25" s="187" t="s">
         <v>571</v>
       </c>
-      <c r="L25" s="129"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="130"/>
+      <c r="L25" s="188"/>
+      <c r="M25" s="188"/>
+      <c r="N25" s="189"/>
       <c r="O25" s="52" t="s">
         <v>460</v>
       </c>
@@ -31154,17 +31598,17 @@
       <c r="G26" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="H26" s="121" t="s">
+      <c r="H26" s="190" t="s">
         <v>571</v>
       </c>
-      <c r="I26" s="129"/>
-      <c r="J26" s="130"/>
-      <c r="K26" s="148" t="s">
+      <c r="I26" s="188"/>
+      <c r="J26" s="189"/>
+      <c r="K26" s="187" t="s">
         <v>571</v>
       </c>
-      <c r="L26" s="129"/>
-      <c r="M26" s="129"/>
-      <c r="N26" s="130"/>
+      <c r="L26" s="188"/>
+      <c r="M26" s="188"/>
+      <c r="N26" s="189"/>
       <c r="O26" s="52" t="s">
         <v>460</v>
       </c>
@@ -31191,17 +31635,17 @@
       <c r="G27" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="H27" s="121" t="s">
+      <c r="H27" s="190" t="s">
         <v>571</v>
       </c>
-      <c r="I27" s="129"/>
-      <c r="J27" s="130"/>
-      <c r="K27" s="148" t="s">
+      <c r="I27" s="188"/>
+      <c r="J27" s="189"/>
+      <c r="K27" s="187" t="s">
         <v>571</v>
       </c>
-      <c r="L27" s="129"/>
-      <c r="M27" s="129"/>
-      <c r="N27" s="130"/>
+      <c r="L27" s="188"/>
+      <c r="M27" s="188"/>
+      <c r="N27" s="189"/>
       <c r="O27" s="52" t="s">
         <v>460</v>
       </c>
@@ -31228,17 +31672,17 @@
       <c r="G28" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="H28" s="121" t="s">
+      <c r="H28" s="190" t="s">
         <v>571</v>
       </c>
-      <c r="I28" s="129"/>
-      <c r="J28" s="130"/>
-      <c r="K28" s="148" t="s">
+      <c r="I28" s="188"/>
+      <c r="J28" s="189"/>
+      <c r="K28" s="187" t="s">
         <v>571</v>
       </c>
-      <c r="L28" s="129"/>
-      <c r="M28" s="129"/>
-      <c r="N28" s="130"/>
+      <c r="L28" s="188"/>
+      <c r="M28" s="188"/>
+      <c r="N28" s="189"/>
       <c r="O28" s="52" t="s">
         <v>460</v>
       </c>
@@ -31253,23 +31697,23 @@
       <c r="C29" s="61" t="s">
         <v>554</v>
       </c>
-      <c r="D29" s="118" t="s">
+      <c r="D29" s="169" t="s">
         <v>465</v>
       </c>
-      <c r="E29" s="118"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="121"/>
-      <c r="H29" s="121" t="s">
+      <c r="E29" s="169"/>
+      <c r="F29" s="169"/>
+      <c r="G29" s="190"/>
+      <c r="H29" s="190" t="s">
         <v>571</v>
       </c>
-      <c r="I29" s="129"/>
-      <c r="J29" s="130"/>
-      <c r="K29" s="148" t="s">
+      <c r="I29" s="188"/>
+      <c r="J29" s="189"/>
+      <c r="K29" s="187" t="s">
         <v>571</v>
       </c>
-      <c r="L29" s="129"/>
-      <c r="M29" s="129"/>
-      <c r="N29" s="130"/>
+      <c r="L29" s="188"/>
+      <c r="M29" s="188"/>
+      <c r="N29" s="189"/>
       <c r="O29" s="52" t="s">
         <v>460</v>
       </c>
@@ -31284,23 +31728,23 @@
       <c r="C30" s="61" t="s">
         <v>555</v>
       </c>
-      <c r="D30" s="118" t="s">
+      <c r="D30" s="169" t="s">
         <v>465</v>
       </c>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="121"/>
-      <c r="H30" s="121" t="s">
+      <c r="E30" s="169"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="190"/>
+      <c r="H30" s="190" t="s">
         <v>455</v>
       </c>
-      <c r="I30" s="129"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="148" t="s">
+      <c r="I30" s="188"/>
+      <c r="J30" s="189"/>
+      <c r="K30" s="187" t="s">
         <v>455</v>
       </c>
-      <c r="L30" s="129"/>
-      <c r="M30" s="129"/>
-      <c r="N30" s="130"/>
+      <c r="L30" s="188"/>
+      <c r="M30" s="188"/>
+      <c r="N30" s="189"/>
       <c r="O30" s="52" t="s">
         <v>460</v>
       </c>
@@ -31315,23 +31759,23 @@
       <c r="C31" s="61" t="s">
         <v>556</v>
       </c>
-      <c r="D31" s="118" t="s">
+      <c r="D31" s="169" t="s">
         <v>465</v>
       </c>
-      <c r="E31" s="118"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="121"/>
-      <c r="H31" s="121" t="s">
+      <c r="E31" s="169"/>
+      <c r="F31" s="169"/>
+      <c r="G31" s="190"/>
+      <c r="H31" s="190" t="s">
         <v>455</v>
       </c>
-      <c r="I31" s="129"/>
-      <c r="J31" s="130"/>
-      <c r="K31" s="148" t="s">
+      <c r="I31" s="188"/>
+      <c r="J31" s="189"/>
+      <c r="K31" s="187" t="s">
         <v>455</v>
       </c>
-      <c r="L31" s="129"/>
-      <c r="M31" s="129"/>
-      <c r="N31" s="130"/>
+      <c r="L31" s="188"/>
+      <c r="M31" s="188"/>
+      <c r="N31" s="189"/>
       <c r="O31" s="52" t="s">
         <v>460</v>
       </c>
@@ -31346,23 +31790,23 @@
       <c r="C32" s="60" t="s">
         <v>557</v>
       </c>
-      <c r="D32" s="146" t="s">
+      <c r="D32" s="195" t="s">
         <v>465</v>
       </c>
-      <c r="E32" s="146"/>
-      <c r="F32" s="146"/>
-      <c r="G32" s="147"/>
-      <c r="H32" s="139" t="s">
+      <c r="E32" s="195"/>
+      <c r="F32" s="195"/>
+      <c r="G32" s="196"/>
+      <c r="H32" s="182" t="s">
         <v>455</v>
       </c>
-      <c r="I32" s="140"/>
-      <c r="J32" s="141"/>
-      <c r="K32" s="149" t="s">
+      <c r="I32" s="171"/>
+      <c r="J32" s="172"/>
+      <c r="K32" s="170" t="s">
         <v>455</v>
       </c>
-      <c r="L32" s="140"/>
-      <c r="M32" s="140"/>
-      <c r="N32" s="141"/>
+      <c r="L32" s="171"/>
+      <c r="M32" s="171"/>
+      <c r="N32" s="172"/>
       <c r="O32" s="100" t="s">
         <v>446</v>
       </c>
@@ -31377,23 +31821,23 @@
       <c r="C33" s="60" t="s">
         <v>558</v>
       </c>
-      <c r="D33" s="146" t="s">
+      <c r="D33" s="195" t="s">
         <v>465</v>
       </c>
-      <c r="E33" s="146"/>
-      <c r="F33" s="146"/>
-      <c r="G33" s="147"/>
-      <c r="H33" s="139" t="s">
+      <c r="E33" s="195"/>
+      <c r="F33" s="195"/>
+      <c r="G33" s="196"/>
+      <c r="H33" s="182" t="s">
         <v>455</v>
       </c>
-      <c r="I33" s="140"/>
-      <c r="J33" s="141"/>
-      <c r="K33" s="149" t="s">
+      <c r="I33" s="171"/>
+      <c r="J33" s="172"/>
+      <c r="K33" s="170" t="s">
         <v>455</v>
       </c>
-      <c r="L33" s="140"/>
-      <c r="M33" s="140"/>
-      <c r="N33" s="141"/>
+      <c r="L33" s="171"/>
+      <c r="M33" s="171"/>
+      <c r="N33" s="172"/>
       <c r="O33" s="100" t="s">
         <v>446</v>
       </c>
@@ -31420,17 +31864,17 @@
       <c r="G34" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="H34" s="139" t="s">
+      <c r="H34" s="182" t="s">
         <v>571</v>
       </c>
-      <c r="I34" s="140"/>
-      <c r="J34" s="141"/>
-      <c r="K34" s="149" t="s">
+      <c r="I34" s="171"/>
+      <c r="J34" s="172"/>
+      <c r="K34" s="170" t="s">
         <v>571</v>
       </c>
-      <c r="L34" s="140"/>
-      <c r="M34" s="140"/>
-      <c r="N34" s="141"/>
+      <c r="L34" s="171"/>
+      <c r="M34" s="171"/>
+      <c r="N34" s="172"/>
       <c r="O34" s="100" t="s">
         <v>446</v>
       </c>
@@ -31457,17 +31901,17 @@
       <c r="G35" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="H35" s="139" t="s">
+      <c r="H35" s="182" t="s">
         <v>571</v>
       </c>
-      <c r="I35" s="140"/>
-      <c r="J35" s="141"/>
-      <c r="K35" s="149" t="s">
+      <c r="I35" s="171"/>
+      <c r="J35" s="172"/>
+      <c r="K35" s="170" t="s">
         <v>571</v>
       </c>
-      <c r="L35" s="140"/>
-      <c r="M35" s="140"/>
-      <c r="N35" s="141"/>
+      <c r="L35" s="171"/>
+      <c r="M35" s="171"/>
+      <c r="N35" s="172"/>
       <c r="O35" s="100" t="s">
         <v>446</v>
       </c>
@@ -31494,17 +31938,17 @@
       <c r="G36" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="H36" s="139" t="s">
+      <c r="H36" s="182" t="s">
         <v>571</v>
       </c>
-      <c r="I36" s="140"/>
-      <c r="J36" s="141"/>
-      <c r="K36" s="149" t="s">
+      <c r="I36" s="171"/>
+      <c r="J36" s="172"/>
+      <c r="K36" s="170" t="s">
         <v>571</v>
       </c>
-      <c r="L36" s="140"/>
-      <c r="M36" s="140"/>
-      <c r="N36" s="141"/>
+      <c r="L36" s="171"/>
+      <c r="M36" s="171"/>
+      <c r="N36" s="172"/>
       <c r="O36" s="100" t="s">
         <v>446</v>
       </c>
@@ -31531,17 +31975,17 @@
       <c r="G37" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="H37" s="157" t="s">
+      <c r="H37" s="183" t="s">
         <v>571</v>
       </c>
-      <c r="I37" s="151"/>
-      <c r="J37" s="152"/>
-      <c r="K37" s="150" t="s">
+      <c r="I37" s="174"/>
+      <c r="J37" s="175"/>
+      <c r="K37" s="173" t="s">
         <v>571</v>
       </c>
-      <c r="L37" s="151"/>
-      <c r="M37" s="151"/>
-      <c r="N37" s="152"/>
+      <c r="L37" s="174"/>
+      <c r="M37" s="174"/>
+      <c r="N37" s="175"/>
       <c r="O37" s="101" t="s">
         <v>446</v>
       </c>
@@ -31561,6 +32005,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="K35:N35"/>
     <mergeCell ref="K36:N36"/>
     <mergeCell ref="K37:N37"/>
     <mergeCell ref="C22:J22"/>
@@ -31577,42 +32057,6 @@
     <mergeCell ref="K28:N28"/>
     <mergeCell ref="K29:N29"/>
     <mergeCell ref="K30:N30"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K34:N34"/>
-    <mergeCell ref="K35:N35"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -31636,722 +32080,722 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="B2" s="171" t="s">
+      <c r="B2" s="213" t="s">
         <v>616</v>
       </c>
-      <c r="C2" s="159" t="s">
+      <c r="C2" s="212" t="s">
         <v>615</v>
       </c>
-      <c r="D2" s="171" t="s">
+      <c r="D2" s="213" t="s">
         <v>373</v>
       </c>
-      <c r="E2" s="159" t="s">
+      <c r="E2" s="212" t="s">
         <v>608</v>
       </c>
-      <c r="F2" s="189"/>
-      <c r="G2" s="189" t="s">
+      <c r="F2" s="210"/>
+      <c r="G2" s="210" t="s">
         <v>631</v>
       </c>
-      <c r="H2" s="189" t="s">
+      <c r="H2" s="210" t="s">
         <v>730</v>
       </c>
-      <c r="I2" s="160" t="s">
+      <c r="I2" s="114" t="s">
         <v>486</v>
       </c>
-      <c r="J2" s="159" t="s">
+      <c r="J2" s="212" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="171"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="161" t="s">
+      <c r="B3" s="213"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="213"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="211"/>
+      <c r="H3" s="211"/>
+      <c r="I3" s="115" t="s">
         <v>479</v>
       </c>
-      <c r="J3" s="159"/>
+      <c r="J3" s="212"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="178" t="s">
+      <c r="B4" s="128" t="s">
         <v>478</v>
       </c>
-      <c r="C4" s="179" t="s">
+      <c r="C4" s="129" t="s">
         <v>575</v>
       </c>
-      <c r="D4" s="180" t="s">
+      <c r="D4" s="130" t="s">
         <v>549</v>
       </c>
-      <c r="E4" s="181" t="s">
+      <c r="E4" s="131" t="s">
         <v>597</v>
       </c>
-      <c r="F4" s="163" t="s">
+      <c r="F4" s="117" t="s">
         <v>628</v>
       </c>
-      <c r="G4" s="163" t="s">
+      <c r="G4" s="117" t="s">
         <v>645</v>
       </c>
-      <c r="H4" s="163" t="s">
+      <c r="H4" s="117" t="s">
         <v>731</v>
       </c>
       <c r="I4" s="74" t="s">
         <v>477</v>
       </c>
-      <c r="J4" s="164" t="s">
+      <c r="J4" s="118" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="186"/>
-      <c r="C5" s="187"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="169"/>
-      <c r="F5" s="163" t="s">
+      <c r="B5" s="136"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="117" t="s">
         <v>629</v>
       </c>
-      <c r="G5" s="163" t="s">
+      <c r="G5" s="117" t="s">
         <v>645</v>
       </c>
-      <c r="H5" s="163" t="s">
+      <c r="H5" s="117" t="s">
         <v>731</v>
       </c>
       <c r="I5" s="74" t="s">
         <v>477</v>
       </c>
-      <c r="J5" s="164" t="s">
+      <c r="J5" s="118" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="178" t="s">
+      <c r="B6" s="128" t="s">
         <v>475</v>
       </c>
-      <c r="C6" s="179" t="s">
+      <c r="C6" s="129" t="s">
         <v>592</v>
       </c>
-      <c r="D6" s="180" t="s">
+      <c r="D6" s="130" t="s">
         <v>550</v>
       </c>
-      <c r="E6" s="181" t="s">
+      <c r="E6" s="131" t="s">
         <v>605</v>
       </c>
-      <c r="F6" s="166" t="s">
+      <c r="F6" s="120" t="s">
         <v>617</v>
       </c>
-      <c r="G6" s="166" t="s">
+      <c r="G6" s="120" t="s">
         <v>645</v>
       </c>
-      <c r="H6" s="166" t="s">
+      <c r="H6" s="120" t="s">
         <v>731</v>
       </c>
-      <c r="I6" s="167" t="s">
+      <c r="I6" s="121" t="s">
         <v>636</v>
       </c>
-      <c r="J6" s="165" t="s">
+      <c r="J6" s="119" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="182"/>
-      <c r="C7" s="183"/>
-      <c r="D7" s="184"/>
-      <c r="E7" s="185"/>
-      <c r="F7" s="166" t="s">
+      <c r="B7" s="132"/>
+      <c r="C7" s="133"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="135"/>
+      <c r="F7" s="120" t="s">
         <v>618</v>
       </c>
-      <c r="G7" s="166" t="s">
+      <c r="G7" s="120" t="s">
         <v>645</v>
       </c>
-      <c r="H7" s="166" t="s">
+      <c r="H7" s="120" t="s">
         <v>731</v>
       </c>
-      <c r="I7" s="167" t="s">
+      <c r="I7" s="121" t="s">
         <v>636</v>
       </c>
-      <c r="J7" s="165" t="s">
+      <c r="J7" s="119" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="182"/>
-      <c r="C8" s="183"/>
-      <c r="D8" s="184"/>
-      <c r="E8" s="185"/>
-      <c r="F8" s="166" t="s">
+      <c r="B8" s="132"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="134"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="120" t="s">
         <v>619</v>
       </c>
-      <c r="G8" s="166" t="s">
+      <c r="G8" s="120" t="s">
         <v>645</v>
       </c>
-      <c r="H8" s="166" t="s">
+      <c r="H8" s="120" t="s">
         <v>731</v>
       </c>
-      <c r="I8" s="167" t="s">
+      <c r="I8" s="121" t="s">
         <v>636</v>
       </c>
-      <c r="J8" s="165" t="s">
+      <c r="J8" s="119" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="182"/>
-      <c r="C9" s="183"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="185"/>
-      <c r="F9" s="163" t="s">
+      <c r="B9" s="132"/>
+      <c r="C9" s="133"/>
+      <c r="D9" s="134"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="117" t="s">
         <v>614</v>
       </c>
-      <c r="G9" s="163" t="s">
+      <c r="G9" s="117" t="s">
         <v>645</v>
       </c>
-      <c r="H9" s="163" t="s">
+      <c r="H9" s="117" t="s">
         <v>731</v>
       </c>
       <c r="I9" s="74" t="s">
         <v>477</v>
       </c>
-      <c r="J9" s="162" t="s">
+      <c r="J9" s="116" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="186"/>
-      <c r="C10" s="187"/>
-      <c r="D10" s="188"/>
-      <c r="E10" s="169"/>
-      <c r="F10" s="163" t="s">
+      <c r="B10" s="136"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="138"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="117" t="s">
         <v>689</v>
       </c>
-      <c r="G10" s="163" t="s">
+      <c r="G10" s="117" t="s">
         <v>645</v>
       </c>
-      <c r="H10" s="163" t="s">
+      <c r="H10" s="117" t="s">
         <v>731</v>
       </c>
       <c r="I10" s="74" t="s">
         <v>477</v>
       </c>
-      <c r="J10" s="162" t="s">
+      <c r="J10" s="116" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="178" t="s">
+      <c r="B11" s="128" t="s">
         <v>473</v>
       </c>
-      <c r="C11" s="179" t="s">
+      <c r="C11" s="129" t="s">
         <v>587</v>
       </c>
-      <c r="D11" s="180" t="s">
+      <c r="D11" s="130" t="s">
         <v>551</v>
       </c>
-      <c r="E11" s="181" t="s">
+      <c r="E11" s="131" t="s">
         <v>468</v>
       </c>
-      <c r="F11" s="163" t="s">
+      <c r="F11" s="117" t="s">
         <v>634</v>
       </c>
-      <c r="G11" s="163" t="s">
+      <c r="G11" s="117" t="s">
         <v>645</v>
       </c>
-      <c r="H11" s="163" t="s">
+      <c r="H11" s="117" t="s">
         <v>731</v>
       </c>
       <c r="I11" s="74" t="s">
         <v>460</v>
       </c>
-      <c r="J11" s="164" t="s">
+      <c r="J11" s="118" t="s">
         <v>638</v>
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="186"/>
-      <c r="C12" s="187"/>
-      <c r="D12" s="188"/>
-      <c r="E12" s="169"/>
-      <c r="F12" s="166" t="s">
+      <c r="B12" s="136"/>
+      <c r="C12" s="137"/>
+      <c r="D12" s="138"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="120" t="s">
         <v>635</v>
       </c>
-      <c r="G12" s="166" t="s">
+      <c r="G12" s="120" t="s">
         <v>646</v>
       </c>
-      <c r="H12" s="166" t="s">
+      <c r="H12" s="120" t="s">
         <v>731</v>
       </c>
-      <c r="I12" s="167" t="s">
+      <c r="I12" s="121" t="s">
         <v>637</v>
       </c>
-      <c r="J12" s="168" t="s">
+      <c r="J12" s="122" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="172" t="s">
+      <c r="B13" s="125" t="s">
         <v>471</v>
       </c>
-      <c r="C13" s="162" t="s">
+      <c r="C13" s="116" t="s">
         <v>573</v>
       </c>
       <c r="D13" s="44" t="s">
         <v>552</v>
       </c>
-      <c r="E13" s="163" t="s">
+      <c r="E13" s="117" t="s">
         <v>595</v>
       </c>
-      <c r="F13" s="163" t="s">
+      <c r="F13" s="117" t="s">
         <v>640</v>
       </c>
-      <c r="G13" s="163" t="s">
+      <c r="G13" s="117" t="s">
         <v>645</v>
       </c>
-      <c r="H13" s="163" t="s">
+      <c r="H13" s="117" t="s">
         <v>731</v>
       </c>
       <c r="I13" s="74" t="s">
         <v>460</v>
       </c>
-      <c r="J13" s="162" t="s">
+      <c r="J13" s="116" t="s">
         <v>641</v>
       </c>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="172" t="s">
+      <c r="B14" s="125" t="s">
         <v>469</v>
       </c>
-      <c r="C14" s="162" t="s">
+      <c r="C14" s="116" t="s">
         <v>574</v>
       </c>
       <c r="D14" s="44" t="s">
         <v>553</v>
       </c>
-      <c r="E14" s="163" t="s">
+      <c r="E14" s="117" t="s">
         <v>596</v>
       </c>
-      <c r="F14" s="163" t="s">
+      <c r="F14" s="117" t="s">
         <v>640</v>
       </c>
-      <c r="G14" s="163" t="s">
+      <c r="G14" s="117" t="s">
         <v>645</v>
       </c>
-      <c r="H14" s="163" t="s">
+      <c r="H14" s="117" t="s">
         <v>731</v>
       </c>
       <c r="I14" s="74" t="s">
         <v>460</v>
       </c>
-      <c r="J14" s="162" t="s">
+      <c r="J14" s="116" t="s">
         <v>642</v>
       </c>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="178" t="s">
+      <c r="B15" s="128" t="s">
         <v>466</v>
       </c>
-      <c r="C15" s="191" t="s">
+      <c r="C15" s="129" t="s">
         <v>582</v>
       </c>
-      <c r="D15" s="180" t="s">
+      <c r="D15" s="130" t="s">
         <v>554</v>
       </c>
-      <c r="E15" s="192" t="s">
+      <c r="E15" s="131" t="s">
         <v>602</v>
       </c>
-      <c r="F15" s="173" t="s">
+      <c r="F15" s="117" t="s">
         <v>643</v>
       </c>
-      <c r="G15" s="173" t="s">
+      <c r="G15" s="117" t="s">
         <v>729</v>
       </c>
-      <c r="H15" s="230" t="s">
+      <c r="H15" s="163" t="s">
         <v>732</v>
       </c>
-      <c r="I15" s="174" t="s">
+      <c r="I15" s="74" t="s">
         <v>460</v>
       </c>
-      <c r="J15" s="175" t="s">
+      <c r="J15" s="118" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="182"/>
-      <c r="C16" s="193"/>
-      <c r="D16" s="184"/>
-      <c r="E16" s="194"/>
-      <c r="F16" s="166" t="s">
+      <c r="B16" s="132"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="120" t="s">
         <v>648</v>
       </c>
-      <c r="G16" s="166" t="s">
+      <c r="G16" s="120" t="s">
         <v>647</v>
       </c>
-      <c r="H16" s="166" t="s">
+      <c r="H16" s="120" t="s">
         <v>731</v>
       </c>
-      <c r="I16" s="167" t="s">
+      <c r="I16" s="121" t="s">
         <v>637</v>
       </c>
-      <c r="J16" s="168" t="s">
+      <c r="J16" s="122" t="s">
         <v>650</v>
       </c>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="186"/>
-      <c r="C17" s="195"/>
-      <c r="D17" s="188"/>
-      <c r="E17" s="196"/>
-      <c r="F17" s="166" t="s">
+      <c r="B17" s="136"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="123"/>
+      <c r="F17" s="120" t="s">
         <v>644</v>
       </c>
-      <c r="G17" s="166" t="s">
+      <c r="G17" s="120" t="s">
         <v>652</v>
       </c>
-      <c r="H17" s="166" t="s">
+      <c r="H17" s="120" t="s">
         <v>731</v>
       </c>
-      <c r="I17" s="167" t="s">
+      <c r="I17" s="121" t="s">
         <v>637</v>
       </c>
-      <c r="J17" s="168" t="s">
+      <c r="J17" s="122" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="18" spans="2:10">
-      <c r="B18" s="172" t="s">
+      <c r="B18" s="125" t="s">
         <v>463</v>
       </c>
-      <c r="C18" s="162" t="s">
+      <c r="C18" s="116" t="s">
         <v>583</v>
       </c>
       <c r="D18" s="44" t="s">
         <v>555</v>
       </c>
-      <c r="E18" s="163" t="s">
+      <c r="E18" s="117" t="s">
         <v>603</v>
       </c>
-      <c r="F18" s="163" t="s">
+      <c r="F18" s="117" t="s">
         <v>653</v>
       </c>
-      <c r="G18" s="173" t="s">
+      <c r="G18" s="117" t="s">
         <v>734</v>
       </c>
-      <c r="H18" s="163" t="s">
+      <c r="H18" s="117" t="s">
         <v>731</v>
       </c>
       <c r="I18" s="74" t="s">
         <v>460</v>
       </c>
-      <c r="J18" s="164" t="s">
+      <c r="J18" s="118" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="178" t="s">
+      <c r="B19" s="128" t="s">
         <v>691</v>
       </c>
-      <c r="C19" s="179" t="s">
+      <c r="C19" s="129" t="s">
         <v>583</v>
       </c>
-      <c r="D19" s="180" t="s">
+      <c r="D19" s="130" t="s">
         <v>556</v>
       </c>
-      <c r="E19" s="181" t="s">
+      <c r="E19" s="131" t="s">
         <v>603</v>
       </c>
-      <c r="F19" s="163" t="s">
+      <c r="F19" s="117" t="s">
         <v>654</v>
       </c>
-      <c r="G19" s="173" t="s">
+      <c r="G19" s="117" t="s">
         <v>734</v>
       </c>
-      <c r="H19" s="181" t="s">
+      <c r="H19" s="131" t="s">
         <v>733</v>
       </c>
-      <c r="I19" s="226"/>
-      <c r="J19" s="227"/>
+      <c r="I19" s="159"/>
+      <c r="J19" s="160"/>
     </row>
     <row r="20" spans="2:10">
-      <c r="B20" s="186"/>
-      <c r="C20" s="187"/>
-      <c r="D20" s="188"/>
-      <c r="E20" s="169" t="s">
+      <c r="B20" s="136"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="123" t="s">
         <v>737</v>
       </c>
-      <c r="F20" s="166" t="s">
+      <c r="F20" s="120" t="s">
         <v>655</v>
       </c>
-      <c r="G20" s="166" t="s">
+      <c r="G20" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="H20" s="166" t="s">
+      <c r="H20" s="120" t="s">
         <v>731</v>
       </c>
-      <c r="I20" s="167" t="s">
+      <c r="I20" s="121" t="s">
         <v>637</v>
       </c>
-      <c r="J20" s="229"/>
+      <c r="J20" s="162"/>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="172" t="s">
+      <c r="B21" s="125" t="s">
         <v>461</v>
       </c>
-      <c r="C21" s="162" t="s">
+      <c r="C21" s="116" t="s">
         <v>585</v>
       </c>
       <c r="D21" s="44" t="s">
         <v>557</v>
       </c>
-      <c r="E21" s="163" t="s">
+      <c r="E21" s="117" t="s">
         <v>604</v>
       </c>
-      <c r="F21" s="163" t="s">
+      <c r="F21" s="117" t="s">
         <v>735</v>
       </c>
-      <c r="G21" s="173" t="s">
+      <c r="G21" s="117" t="s">
         <v>734</v>
       </c>
-      <c r="H21" s="181" t="s">
+      <c r="H21" s="131" t="s">
         <v>733</v>
       </c>
       <c r="I21" s="74" t="s">
         <v>460</v>
       </c>
-      <c r="J21" s="164" t="s">
+      <c r="J21" s="118" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="178" t="s">
+      <c r="B22" s="128" t="s">
         <v>692</v>
       </c>
-      <c r="C22" s="179" t="s">
+      <c r="C22" s="129" t="s">
         <v>585</v>
       </c>
-      <c r="D22" s="180" t="s">
+      <c r="D22" s="130" t="s">
         <v>558</v>
       </c>
-      <c r="E22" s="181"/>
-      <c r="F22" s="163" t="s">
+      <c r="E22" s="131"/>
+      <c r="F22" s="117" t="s">
         <v>736</v>
       </c>
-      <c r="G22" s="173" t="s">
+      <c r="G22" s="117" t="s">
         <v>734</v>
       </c>
-      <c r="H22" s="163"/>
+      <c r="H22" s="117"/>
       <c r="I22" s="74"/>
-      <c r="J22" s="164"/>
+      <c r="J22" s="118"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="186"/>
-      <c r="C23" s="187"/>
-      <c r="D23" s="188"/>
-      <c r="E23" s="169"/>
-      <c r="F23" s="166" t="s">
+      <c r="B23" s="136"/>
+      <c r="C23" s="137"/>
+      <c r="D23" s="138"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="120" t="s">
         <v>738</v>
       </c>
-      <c r="G23" s="166" t="s">
+      <c r="G23" s="120" t="s">
         <v>734</v>
       </c>
-      <c r="H23" s="166" t="s">
+      <c r="H23" s="120" t="s">
         <v>731</v>
       </c>
-      <c r="I23" s="167" t="s">
+      <c r="I23" s="121" t="s">
         <v>637</v>
       </c>
-      <c r="J23" s="168"/>
+      <c r="J23" s="122"/>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="176" t="s">
+      <c r="B24" s="126" t="s">
         <v>458</v>
       </c>
-      <c r="C24" s="165" t="s">
+      <c r="C24" s="119" t="s">
         <v>588</v>
       </c>
-      <c r="D24" s="177" t="s">
+      <c r="D24" s="127" t="s">
         <v>559</v>
       </c>
-      <c r="E24" s="166" t="s">
+      <c r="E24" s="120" t="s">
         <v>606</v>
       </c>
-      <c r="F24" s="166" t="s">
+      <c r="F24" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="G24" s="166" t="s">
+      <c r="G24" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="H24" s="166" t="s">
+      <c r="H24" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="167" t="s">
+      <c r="I24" s="121" t="s">
         <v>446</v>
       </c>
-      <c r="J24" s="165" t="s">
+      <c r="J24" s="119" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="30">
-      <c r="B25" s="176" t="s">
+      <c r="B25" s="126" t="s">
         <v>456</v>
       </c>
-      <c r="C25" s="165" t="s">
+      <c r="C25" s="119" t="s">
         <v>590</v>
       </c>
-      <c r="D25" s="177" t="s">
+      <c r="D25" s="127" t="s">
         <v>560</v>
       </c>
-      <c r="E25" s="166" t="s">
+      <c r="E25" s="120" t="s">
         <v>607</v>
       </c>
-      <c r="F25" s="166" t="s">
+      <c r="F25" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="166" t="s">
+      <c r="G25" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="H25" s="166" t="s">
+      <c r="H25" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="I25" s="167" t="s">
+      <c r="I25" s="121" t="s">
         <v>446</v>
       </c>
-      <c r="J25" s="165" t="s">
+      <c r="J25" s="119" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="26" spans="2:10">
-      <c r="B26" s="176" t="s">
+      <c r="B26" s="126" t="s">
         <v>453</v>
       </c>
-      <c r="C26" s="165" t="s">
+      <c r="C26" s="119" t="s">
         <v>578</v>
       </c>
-      <c r="D26" s="177" t="s">
+      <c r="D26" s="127" t="s">
         <v>561</v>
       </c>
-      <c r="E26" s="166" t="s">
+      <c r="E26" s="120" t="s">
         <v>600</v>
       </c>
-      <c r="F26" s="166" t="s">
+      <c r="F26" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="G26" s="166" t="s">
+      <c r="G26" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="H26" s="166" t="s">
+      <c r="H26" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="I26" s="167" t="s">
+      <c r="I26" s="121" t="s">
         <v>446</v>
       </c>
-      <c r="J26" s="168" t="s">
+      <c r="J26" s="122" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="30">
-      <c r="B27" s="176" t="s">
+      <c r="B27" s="126" t="s">
         <v>451</v>
       </c>
-      <c r="C27" s="165" t="s">
+      <c r="C27" s="119" t="s">
         <v>580</v>
       </c>
-      <c r="D27" s="177" t="s">
+      <c r="D27" s="127" t="s">
         <v>562</v>
       </c>
-      <c r="E27" s="166" t="s">
+      <c r="E27" s="120" t="s">
         <v>601</v>
       </c>
-      <c r="F27" s="166" t="s">
+      <c r="F27" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="166" t="s">
+      <c r="G27" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="H27" s="166" t="s">
+      <c r="H27" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="I27" s="167" t="s">
+      <c r="I27" s="121" t="s">
         <v>446</v>
       </c>
-      <c r="J27" s="165" t="s">
+      <c r="J27" s="119" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="28" spans="2:10">
-      <c r="B28" s="176" t="s">
+      <c r="B28" s="126" t="s">
         <v>449</v>
       </c>
-      <c r="C28" s="165" t="s">
+      <c r="C28" s="119" t="s">
         <v>576</v>
       </c>
-      <c r="D28" s="177" t="s">
+      <c r="D28" s="127" t="s">
         <v>693</v>
       </c>
-      <c r="E28" s="166" t="s">
+      <c r="E28" s="120" t="s">
         <v>598</v>
       </c>
-      <c r="F28" s="166" t="s">
+      <c r="F28" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="G28" s="166" t="s">
+      <c r="G28" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="H28" s="166" t="s">
+      <c r="H28" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="I28" s="167" t="s">
+      <c r="I28" s="121" t="s">
         <v>446</v>
       </c>
-      <c r="J28" s="168" t="s">
+      <c r="J28" s="122" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="29" spans="2:10" ht="30">
-      <c r="B29" s="176" t="s">
+      <c r="B29" s="126" t="s">
         <v>447</v>
       </c>
-      <c r="C29" s="165" t="s">
+      <c r="C29" s="119" t="s">
         <v>577</v>
       </c>
-      <c r="D29" s="177" t="s">
+      <c r="D29" s="127" t="s">
         <v>694</v>
       </c>
-      <c r="E29" s="166" t="s">
+      <c r="E29" s="120" t="s">
         <v>599</v>
       </c>
-      <c r="F29" s="166" t="s">
+      <c r="F29" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="G29" s="166" t="s">
+      <c r="G29" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="H29" s="166" t="s">
+      <c r="H29" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="I29" s="167" t="s">
+      <c r="I29" s="121" t="s">
         <v>446</v>
       </c>
-      <c r="J29" s="168" t="s">
+      <c r="J29" s="122" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="32" spans="2:10">
-      <c r="E32" s="170" t="s">
+      <c r="E32" s="124" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="33" spans="3:5">
-      <c r="E33" s="170" t="s">
+      <c r="E33" s="124" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="34" spans="3:5">
-      <c r="E34" s="170" t="s">
+      <c r="E34" s="124" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="35" spans="3:5">
-      <c r="E35" s="170" t="s">
+      <c r="E35" s="124" t="s">
         <v>627</v>
       </c>
     </row>
@@ -32618,7 +33062,7 @@
       <c r="E5" t="s">
         <v>305</v>
       </c>
-      <c r="F5" s="228" t="s">
+      <c r="F5" s="161" t="s">
         <v>727</v>
       </c>
     </row>
@@ -32632,8 +33076,78 @@
       <c r="E6" t="s">
         <v>726</v>
       </c>
-      <c r="F6" s="228" t="s">
+      <c r="F6" s="161" t="s">
         <v>728</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442C776A-DBB8-40FA-BC0F-185BDFB3E008}">
+  <dimension ref="C6:C18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="6" spans="3:3">
+      <c r="C6" s="214" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" s="215" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" s="215" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3">
+      <c r="C9" s="216" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" s="216" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3">
+      <c r="C11" s="216" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" s="216" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="13" spans="3:3">
+      <c r="C13" s="216" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" s="216" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="15" spans="3:3">
+      <c r="C15" s="216" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="214" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="215" t="s">
+        <v>749</v>
       </c>
     </row>
   </sheetData>
@@ -33304,102 +33818,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="164" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
     </row>
     <row r="2" spans="1:22" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="114"/>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
+      <c r="A2" s="164"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
     </row>
     <row r="3" spans="1:22" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="114"/>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
+      <c r="A3" s="164"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
     </row>
     <row r="4" spans="1:22" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A4" s="114"/>
-      <c r="B4" s="114"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
+      <c r="A4" s="164"/>
+      <c r="B4" s="164"/>
+      <c r="C4" s="164"/>
+      <c r="D4" s="164"/>
+      <c r="E4" s="164"/>
+      <c r="F4" s="164"/>
     </row>
     <row r="5" spans="1:22" s="13" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A5" s="114"/>
-      <c r="B5" s="114"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
+      <c r="A5" s="164"/>
+      <c r="B5" s="164"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="164"/>
+      <c r="E5" s="164"/>
+      <c r="F5" s="164"/>
     </row>
     <row r="6" spans="1:22" ht="28.5" customHeight="1">
-      <c r="A6" s="202" t="s">
+      <c r="A6" s="143" t="s">
         <v>156</v>
       </c>
-      <c r="B6" s="202" t="s">
+      <c r="B6" s="143" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="202" t="s">
+      <c r="C6" s="143" t="s">
         <v>154</v>
       </c>
-      <c r="D6" s="202" t="s">
+      <c r="D6" s="143" t="s">
         <v>153</v>
       </c>
-      <c r="E6" s="202" t="s">
+      <c r="E6" s="143" t="s">
         <v>152</v>
       </c>
-      <c r="F6" s="201" t="s">
+      <c r="F6" s="142" t="s">
         <v>151</v>
       </c>
-      <c r="G6" s="203"/>
-      <c r="H6" s="199" t="s">
+      <c r="G6" s="144"/>
+      <c r="H6" s="140" t="s">
         <v>656</v>
       </c>
-      <c r="I6" s="204"/>
-      <c r="J6" s="201" t="s">
+      <c r="I6" s="145"/>
+      <c r="J6" s="142" t="s">
         <v>3</v>
       </c>
-      <c r="K6" s="201" t="s">
+      <c r="K6" s="142" t="s">
         <v>165</v>
       </c>
-      <c r="L6" s="201" t="s">
+      <c r="L6" s="142" t="s">
         <v>170</v>
       </c>
-      <c r="M6" s="201" t="s">
+      <c r="M6" s="142" t="s">
         <v>666</v>
       </c>
-      <c r="N6" s="201" t="s">
+      <c r="N6" s="142" t="s">
         <v>167</v>
       </c>
-      <c r="O6" s="201" t="s">
+      <c r="O6" s="142" t="s">
         <v>685</v>
       </c>
-      <c r="P6" s="201" t="s">
+      <c r="P6" s="142" t="s">
         <v>667</v>
       </c>
-      <c r="Q6" s="201" t="s">
+      <c r="Q6" s="142" t="s">
         <v>687</v>
       </c>
-      <c r="R6" s="201" t="s">
+      <c r="R6" s="142" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="201" t="s">
+      <c r="S6" s="142" t="s">
         <v>168</v>
       </c>
-      <c r="T6" s="201" t="s">
+      <c r="T6" s="142" t="s">
         <v>232</v>
       </c>
     </row>
@@ -33428,20 +33942,20 @@
       <c r="K7" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="L7" s="197" t="s">
+      <c r="L7" s="139" t="s">
         <v>74</v>
       </c>
-      <c r="M7" s="200" t="s">
+      <c r="M7" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N7" s="18" t="s">
         <v>216</v>
       </c>
       <c r="O7" s="18"/>
-      <c r="P7" s="200" t="s">
+      <c r="P7" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q7" s="199"/>
+      <c r="Q7" s="140"/>
       <c r="R7" s="14">
         <v>1</v>
       </c>
@@ -33479,20 +33993,20 @@
       <c r="K8" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="L8" s="197" t="s">
+      <c r="L8" s="139" t="s">
         <v>74</v>
       </c>
-      <c r="M8" s="200" t="s">
+      <c r="M8" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N8" s="18" t="s">
         <v>217</v>
       </c>
       <c r="O8" s="18"/>
-      <c r="P8" s="200" t="s">
+      <c r="P8" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q8" s="199"/>
+      <c r="Q8" s="140"/>
       <c r="R8" s="14">
         <v>2</v>
       </c>
@@ -33532,20 +34046,20 @@
       <c r="K9" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="L9" s="197" t="s">
+      <c r="L9" s="139" t="s">
         <v>74</v>
       </c>
-      <c r="M9" s="200" t="s">
+      <c r="M9" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N9" s="18" t="s">
         <v>218</v>
       </c>
       <c r="O9" s="18"/>
-      <c r="P9" s="200" t="s">
+      <c r="P9" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q9" s="199"/>
+      <c r="Q9" s="140"/>
       <c r="R9" s="14">
         <v>3</v>
       </c>
@@ -33585,20 +34099,20 @@
       <c r="K10" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="L10" s="197" t="s">
+      <c r="L10" s="139" t="s">
         <v>74</v>
       </c>
-      <c r="M10" s="200" t="s">
+      <c r="M10" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N10" s="18" t="s">
         <v>41</v>
       </c>
       <c r="O10" s="18"/>
-      <c r="P10" s="200" t="s">
+      <c r="P10" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q10" s="199"/>
+      <c r="Q10" s="140"/>
       <c r="R10" s="14">
         <v>4</v>
       </c>
@@ -33636,20 +34150,20 @@
       <c r="K11" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="L11" s="197" t="s">
+      <c r="L11" s="139" t="s">
         <v>74</v>
       </c>
-      <c r="M11" s="200" t="s">
+      <c r="M11" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N11" s="18" t="s">
         <v>214</v>
       </c>
       <c r="O11" s="18"/>
-      <c r="P11" s="200" t="s">
+      <c r="P11" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q11" s="199"/>
+      <c r="Q11" s="140"/>
       <c r="R11" s="14">
         <v>5</v>
       </c>
@@ -33679,33 +34193,33 @@
         <v>59</v>
       </c>
       <c r="I12" s="13"/>
-      <c r="J12" s="217">
+      <c r="J12" s="151">
         <v>6</v>
       </c>
-      <c r="K12" s="213" t="s">
+      <c r="K12" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="L12" s="214" t="s">
+      <c r="L12" s="148" t="s">
         <v>74</v>
       </c>
-      <c r="M12" s="216" t="s">
+      <c r="M12" s="150" t="s">
         <v>93</v>
       </c>
-      <c r="N12" s="213" t="s">
+      <c r="N12" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="O12" s="213"/>
-      <c r="P12" s="216" t="s">
+      <c r="O12" s="147"/>
+      <c r="P12" s="150" t="s">
         <v>659</v>
       </c>
-      <c r="Q12" s="215"/>
-      <c r="R12" s="217">
+      <c r="Q12" s="149"/>
+      <c r="R12" s="151">
         <v>6</v>
       </c>
-      <c r="S12" s="213" t="s">
+      <c r="S12" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="T12" s="213" t="s">
+      <c r="T12" s="147" t="s">
         <v>660</v>
       </c>
       <c r="V12" s="9" t="str">
@@ -33735,28 +34249,28 @@
       <c r="J13" s="14">
         <v>7</v>
       </c>
-      <c r="K13" s="209" t="s">
+      <c r="K13" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="L13" s="210">
+      <c r="L13" s="139">
         <v>3</v>
       </c>
-      <c r="M13" s="211"/>
-      <c r="N13" s="209" t="s">
+      <c r="M13" s="141"/>
+      <c r="N13" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="O13" s="209"/>
-      <c r="P13" s="211" t="s">
+      <c r="O13" s="18"/>
+      <c r="P13" s="141" t="s">
         <v>658</v>
       </c>
-      <c r="Q13" s="212"/>
+      <c r="Q13" s="140"/>
       <c r="R13" s="14">
         <v>7</v>
       </c>
-      <c r="S13" s="209" t="s">
+      <c r="S13" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="T13" s="209" t="s">
+      <c r="T13" s="18" t="s">
         <v>272</v>
       </c>
       <c r="V13" s="9" t="str">
@@ -33779,33 +34293,33 @@
         <v>63</v>
       </c>
       <c r="I14" s="13"/>
-      <c r="J14" s="217">
+      <c r="J14" s="151">
         <v>8</v>
       </c>
-      <c r="K14" s="213" t="s">
+      <c r="K14" s="147" t="s">
         <v>92</v>
       </c>
-      <c r="L14" s="214" t="s">
+      <c r="L14" s="148" t="s">
         <v>74</v>
       </c>
-      <c r="M14" s="216" t="s">
+      <c r="M14" s="150" t="s">
         <v>93</v>
       </c>
-      <c r="N14" s="213" t="s">
+      <c r="N14" s="147" t="s">
         <v>92</v>
       </c>
-      <c r="O14" s="213"/>
-      <c r="P14" s="216" t="s">
+      <c r="O14" s="147"/>
+      <c r="P14" s="150" t="s">
         <v>659</v>
       </c>
-      <c r="Q14" s="215"/>
-      <c r="R14" s="217">
+      <c r="Q14" s="149"/>
+      <c r="R14" s="151">
         <v>8</v>
       </c>
-      <c r="S14" s="213" t="s">
+      <c r="S14" s="147" t="s">
         <v>92</v>
       </c>
-      <c r="T14" s="213" t="s">
+      <c r="T14" s="147" t="s">
         <v>660</v>
       </c>
       <c r="V14" s="9" t="str">
@@ -33835,28 +34349,28 @@
       <c r="J15" s="14">
         <v>9</v>
       </c>
-      <c r="K15" s="209" t="s">
+      <c r="K15" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="L15" s="210">
+      <c r="L15" s="139">
         <v>2</v>
       </c>
-      <c r="M15" s="211"/>
-      <c r="N15" s="209" t="s">
+      <c r="M15" s="141"/>
+      <c r="N15" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="O15" s="209"/>
-      <c r="P15" s="211" t="s">
+      <c r="O15" s="18"/>
+      <c r="P15" s="141" t="s">
         <v>658</v>
       </c>
-      <c r="Q15" s="212"/>
+      <c r="Q15" s="140"/>
       <c r="R15" s="14">
         <v>9</v>
       </c>
-      <c r="S15" s="209" t="s">
+      <c r="S15" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="T15" s="209" t="s">
+      <c r="T15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="V15" s="9" t="str">
@@ -33887,22 +34401,22 @@
       <c r="K16" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="L16" s="197" t="s">
+      <c r="L16" s="139" t="s">
         <v>74</v>
       </c>
-      <c r="M16" s="200" t="s">
+      <c r="M16" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N16" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="O16" s="206" t="s">
+      <c r="O16" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P16" s="200" t="s">
+      <c r="P16" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q16" s="199"/>
+      <c r="Q16" s="140"/>
       <c r="R16" s="14">
         <v>10</v>
       </c>
@@ -33942,22 +34456,22 @@
       <c r="K17" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="L17" s="197" t="s">
+      <c r="L17" s="139" t="s">
         <v>74</v>
       </c>
-      <c r="M17" s="200" t="s">
+      <c r="M17" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N17" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="O17" s="206" t="s">
+      <c r="O17" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P17" s="200" t="s">
+      <c r="P17" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q17" s="199"/>
+      <c r="Q17" s="140"/>
       <c r="R17" s="14">
         <v>11</v>
       </c>
@@ -33997,22 +34511,22 @@
       <c r="K18" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="L18" s="197" t="s">
+      <c r="L18" s="139" t="s">
         <v>74</v>
       </c>
-      <c r="M18" s="200" t="s">
+      <c r="M18" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N18" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="O18" s="206" t="s">
+      <c r="O18" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P18" s="200" t="s">
+      <c r="P18" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q18" s="199"/>
+      <c r="Q18" s="140"/>
       <c r="R18" s="14">
         <v>12</v>
       </c>
@@ -34050,22 +34564,22 @@
       <c r="K19" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="L19" s="197">
+      <c r="L19" s="139">
         <v>4</v>
       </c>
-      <c r="M19" s="205" t="s">
+      <c r="M19" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N19" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="O19" s="206" t="s">
+      <c r="O19" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P19" s="207" t="s">
+      <c r="P19" s="141" t="s">
         <v>658</v>
       </c>
-      <c r="Q19" s="208" t="s">
+      <c r="Q19" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R19" s="14">
@@ -34101,35 +34615,35 @@
         <v>13</v>
       </c>
       <c r="I20" s="13"/>
-      <c r="J20" s="220">
+      <c r="J20" s="153">
         <v>14</v>
       </c>
-      <c r="K20" s="221" t="s">
+      <c r="K20" s="154" t="s">
         <v>173</v>
       </c>
-      <c r="L20" s="222">
+      <c r="L20" s="155">
         <v>1</v>
       </c>
-      <c r="M20" s="223" t="s">
+      <c r="M20" s="156" t="s">
         <v>657</v>
       </c>
-      <c r="N20" s="221" t="s">
+      <c r="N20" s="154" t="s">
         <v>174</v>
       </c>
-      <c r="O20" s="224" t="s">
+      <c r="O20" s="157" t="s">
         <v>74</v>
       </c>
-      <c r="P20" s="223" t="s">
+      <c r="P20" s="156" t="s">
         <v>659</v>
       </c>
-      <c r="Q20" s="225"/>
-      <c r="R20" s="220">
+      <c r="Q20" s="158"/>
+      <c r="R20" s="153">
         <v>14</v>
       </c>
-      <c r="S20" s="221" t="s">
+      <c r="S20" s="154" t="s">
         <v>142</v>
       </c>
-      <c r="T20" s="221" t="s">
+      <c r="T20" s="154" t="s">
         <v>233</v>
       </c>
       <c r="V20" s="9" t="str">
@@ -34156,35 +34670,35 @@
         <v>14</v>
       </c>
       <c r="I21" s="13"/>
-      <c r="J21" s="220">
+      <c r="J21" s="153">
         <v>15</v>
       </c>
-      <c r="K21" s="221" t="s">
+      <c r="K21" s="154" t="s">
         <v>173</v>
       </c>
-      <c r="L21" s="222">
+      <c r="L21" s="155">
         <v>19</v>
       </c>
-      <c r="M21" s="223" t="s">
+      <c r="M21" s="156" t="s">
         <v>657</v>
       </c>
-      <c r="N21" s="221" t="s">
+      <c r="N21" s="154" t="s">
         <v>174</v>
       </c>
-      <c r="O21" s="224" t="s">
+      <c r="O21" s="157" t="s">
         <v>74</v>
       </c>
-      <c r="P21" s="223" t="s">
+      <c r="P21" s="156" t="s">
         <v>659</v>
       </c>
-      <c r="Q21" s="225"/>
-      <c r="R21" s="220">
+      <c r="Q21" s="158"/>
+      <c r="R21" s="153">
         <v>15</v>
       </c>
-      <c r="S21" s="221" t="s">
+      <c r="S21" s="154" t="s">
         <v>141</v>
       </c>
-      <c r="T21" s="221" t="s">
+      <c r="T21" s="154" t="s">
         <v>233</v>
       </c>
       <c r="V21" s="9" t="str">
@@ -34211,35 +34725,35 @@
         <v>15</v>
       </c>
       <c r="I22" s="13"/>
-      <c r="J22" s="220">
+      <c r="J22" s="153">
         <v>16</v>
       </c>
-      <c r="K22" s="221" t="s">
+      <c r="K22" s="154" t="s">
         <v>173</v>
       </c>
-      <c r="L22" s="222">
+      <c r="L22" s="155">
         <v>20</v>
       </c>
-      <c r="M22" s="223" t="s">
+      <c r="M22" s="156" t="s">
         <v>657</v>
       </c>
-      <c r="N22" s="221" t="s">
+      <c r="N22" s="154" t="s">
         <v>174</v>
       </c>
-      <c r="O22" s="224" t="s">
+      <c r="O22" s="157" t="s">
         <v>74</v>
       </c>
-      <c r="P22" s="223" t="s">
+      <c r="P22" s="156" t="s">
         <v>659</v>
       </c>
-      <c r="Q22" s="225"/>
-      <c r="R22" s="220">
+      <c r="Q22" s="158"/>
+      <c r="R22" s="153">
         <v>16</v>
       </c>
-      <c r="S22" s="221" t="s">
+      <c r="S22" s="154" t="s">
         <v>140</v>
       </c>
-      <c r="T22" s="221" t="s">
+      <c r="T22" s="154" t="s">
         <v>233</v>
       </c>
       <c r="V22" s="9" t="str">
@@ -34266,35 +34780,35 @@
         <v>16</v>
       </c>
       <c r="I23" s="13"/>
-      <c r="J23" s="220">
+      <c r="J23" s="153">
         <v>17</v>
       </c>
-      <c r="K23" s="221" t="s">
+      <c r="K23" s="154" t="s">
         <v>173</v>
       </c>
-      <c r="L23" s="222">
+      <c r="L23" s="155">
         <v>18</v>
       </c>
-      <c r="M23" s="223" t="s">
+      <c r="M23" s="156" t="s">
         <v>658</v>
       </c>
-      <c r="N23" s="221" t="s">
+      <c r="N23" s="154" t="s">
         <v>174</v>
       </c>
-      <c r="O23" s="224" t="s">
+      <c r="O23" s="157" t="s">
         <v>74</v>
       </c>
-      <c r="P23" s="223" t="s">
+      <c r="P23" s="156" t="s">
         <v>659</v>
       </c>
-      <c r="Q23" s="225"/>
-      <c r="R23" s="220">
+      <c r="Q23" s="158"/>
+      <c r="R23" s="153">
         <v>17</v>
       </c>
-      <c r="S23" s="221" t="s">
+      <c r="S23" s="154" t="s">
         <v>139</v>
       </c>
-      <c r="T23" s="221" t="s">
+      <c r="T23" s="154" t="s">
         <v>233</v>
       </c>
       <c r="V23" s="9" t="str">
@@ -34327,22 +34841,22 @@
       <c r="K24" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="L24" s="197">
+      <c r="L24" s="139">
         <v>7</v>
       </c>
-      <c r="M24" s="200" t="s">
+      <c r="M24" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N24" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="O24" s="206" t="s">
+      <c r="O24" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P24" s="200" t="s">
+      <c r="P24" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q24" s="199"/>
+      <c r="Q24" s="140"/>
       <c r="R24" s="14">
         <v>18</v>
       </c>
@@ -34382,22 +34896,22 @@
       <c r="K25" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="L25" s="197">
+      <c r="L25" s="139">
         <v>6</v>
       </c>
-      <c r="M25" s="200" t="s">
+      <c r="M25" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N25" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="O25" s="206" t="s">
+      <c r="O25" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P25" s="200" t="s">
+      <c r="P25" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q25" s="199"/>
+      <c r="Q25" s="140"/>
       <c r="R25" s="14">
         <v>19</v>
       </c>
@@ -34435,22 +34949,22 @@
       <c r="K26" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="L26" s="197">
+      <c r="L26" s="139">
         <v>5</v>
       </c>
-      <c r="M26" s="200" t="s">
+      <c r="M26" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N26" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="O26" s="206" t="s">
+      <c r="O26" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P26" s="200" t="s">
+      <c r="P26" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q26" s="199"/>
+      <c r="Q26" s="140"/>
       <c r="R26" s="14">
         <v>20</v>
       </c>
@@ -34488,22 +35002,22 @@
       <c r="K27" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="L27" s="197">
+      <c r="L27" s="139">
         <v>3</v>
       </c>
-      <c r="M27" s="200" t="s">
+      <c r="M27" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N27" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="O27" s="206" t="s">
+      <c r="O27" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P27" s="200" t="s">
+      <c r="P27" s="141" t="s">
         <v>658</v>
       </c>
-      <c r="Q27" s="199"/>
+      <c r="Q27" s="140"/>
       <c r="R27" s="14">
         <v>21</v>
       </c>
@@ -34541,22 +35055,22 @@
       <c r="K28" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="L28" s="197">
+      <c r="L28" s="139">
         <v>2</v>
       </c>
-      <c r="M28" s="200" t="s">
+      <c r="M28" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N28" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="O28" s="206" t="s">
+      <c r="O28" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P28" s="200" t="s">
+      <c r="P28" s="141" t="s">
         <v>658</v>
       </c>
-      <c r="Q28" s="199"/>
+      <c r="Q28" s="140"/>
       <c r="R28" s="14">
         <v>22</v>
       </c>
@@ -34584,35 +35098,35 @@
         <v>60</v>
       </c>
       <c r="I29" s="13"/>
-      <c r="J29" s="217">
+      <c r="J29" s="151">
         <v>23</v>
       </c>
-      <c r="K29" s="213" t="s">
+      <c r="K29" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="L29" s="214" t="s">
+      <c r="L29" s="148" t="s">
         <v>74</v>
       </c>
-      <c r="M29" s="216" t="s">
+      <c r="M29" s="150" t="s">
         <v>93</v>
       </c>
-      <c r="N29" s="213" t="s">
+      <c r="N29" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="O29" s="215" t="s">
+      <c r="O29" s="149" t="s">
         <v>74</v>
       </c>
-      <c r="P29" s="216" t="s">
+      <c r="P29" s="150" t="s">
         <v>659</v>
       </c>
-      <c r="Q29" s="215"/>
-      <c r="R29" s="217">
+      <c r="Q29" s="149"/>
+      <c r="R29" s="151">
         <v>23</v>
       </c>
-      <c r="S29" s="213" t="s">
+      <c r="S29" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="T29" s="213" t="s">
+      <c r="T29" s="147" t="s">
         <v>660</v>
       </c>
       <c r="V29" s="9" t="str">
@@ -34645,10 +35159,10 @@
       <c r="K30" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L30" s="197">
+      <c r="L30" s="139">
         <v>40</v>
       </c>
-      <c r="M30" s="200" t="s">
+      <c r="M30" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N30" s="18" t="s">
@@ -34657,10 +35171,10 @@
       <c r="O30" s="18" t="s">
         <v>668</v>
       </c>
-      <c r="P30" s="200" t="s">
+      <c r="P30" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q30" s="208" t="s">
+      <c r="Q30" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R30" s="14">
@@ -34700,22 +35214,22 @@
       <c r="K31" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L31" s="197">
+      <c r="L31" s="139">
         <v>37</v>
       </c>
-      <c r="M31" s="200" t="s">
+      <c r="M31" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N31" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O31" s="199" t="s">
+      <c r="O31" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P31" s="200" t="s">
+      <c r="P31" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q31" s="208" t="s">
+      <c r="Q31" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R31" s="14">
@@ -34757,10 +35271,10 @@
       <c r="K32" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L32" s="197">
+      <c r="L32" s="139">
         <v>38</v>
       </c>
-      <c r="M32" s="200" t="s">
+      <c r="M32" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N32" s="18" t="s">
@@ -34769,10 +35283,10 @@
       <c r="O32" s="18" t="s">
         <v>669</v>
       </c>
-      <c r="P32" s="200" t="s">
+      <c r="P32" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q32" s="208" t="s">
+      <c r="Q32" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R32" s="14">
@@ -34814,22 +35328,22 @@
       <c r="K33" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L33" s="197">
+      <c r="L33" s="139">
         <v>36</v>
       </c>
-      <c r="M33" s="200" t="s">
+      <c r="M33" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N33" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O33" s="199" t="s">
+      <c r="O33" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P33" s="200" t="s">
+      <c r="P33" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q33" s="208" t="s">
+      <c r="Q33" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R33" s="14">
@@ -34867,27 +35381,27 @@
         <v>26</v>
       </c>
       <c r="I34" s="13"/>
-      <c r="J34" s="218">
+      <c r="J34" s="14">
         <v>28</v>
       </c>
-      <c r="K34" s="219" t="s">
+      <c r="K34" s="152" t="s">
         <v>663</v>
       </c>
-      <c r="L34" s="210"/>
-      <c r="M34" s="211"/>
-      <c r="N34" s="209"/>
-      <c r="O34" s="209"/>
-      <c r="P34" s="211" t="s">
+      <c r="L34" s="139"/>
+      <c r="M34" s="141"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q34" s="212"/>
-      <c r="R34" s="218">
+      <c r="Q34" s="140"/>
+      <c r="R34" s="14">
         <v>28</v>
       </c>
-      <c r="S34" s="209" t="s">
+      <c r="S34" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="T34" s="209"/>
+      <c r="T34" s="18"/>
       <c r="V34" s="9" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">	output	logic	DEV_OE,</v>
@@ -34914,27 +35428,27 @@
         <v>27</v>
       </c>
       <c r="I35" s="13"/>
-      <c r="J35" s="218">
+      <c r="J35" s="14">
         <v>29</v>
       </c>
-      <c r="K35" s="219" t="s">
+      <c r="K35" s="152" t="s">
         <v>663</v>
       </c>
-      <c r="L35" s="210"/>
-      <c r="M35" s="211"/>
-      <c r="N35" s="209"/>
-      <c r="O35" s="209"/>
-      <c r="P35" s="211" t="s">
+      <c r="L35" s="139"/>
+      <c r="M35" s="141"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q35" s="212"/>
-      <c r="R35" s="218">
+      <c r="Q35" s="140"/>
+      <c r="R35" s="14">
         <v>29</v>
       </c>
-      <c r="S35" s="209" t="s">
+      <c r="S35" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="T35" s="209"/>
+      <c r="T35" s="18"/>
       <c r="V35" s="9" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">	output	logic	DEV_CLRn,</v>
@@ -34965,10 +35479,10 @@
       <c r="K36" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L36" s="197">
+      <c r="L36" s="139">
         <v>35</v>
       </c>
-      <c r="M36" s="200" t="s">
+      <c r="M36" s="141" t="s">
         <v>688</v>
       </c>
       <c r="N36" s="18" t="s">
@@ -34977,10 +35491,10 @@
       <c r="O36" s="18" t="s">
         <v>670</v>
       </c>
-      <c r="P36" s="200" t="s">
+      <c r="P36" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q36" s="208" t="s">
+      <c r="Q36" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R36" s="14">
@@ -35022,10 +35536,10 @@
       <c r="K37" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L37" s="197">
+      <c r="L37" s="139">
         <v>33</v>
       </c>
-      <c r="M37" s="200" t="s">
+      <c r="M37" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N37" s="18" t="s">
@@ -35034,10 +35548,10 @@
       <c r="O37" s="18" t="s">
         <v>671</v>
       </c>
-      <c r="P37" s="200" t="s">
+      <c r="P37" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q37" s="208" t="s">
+      <c r="Q37" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R37" s="14">
@@ -35079,22 +35593,22 @@
       <c r="K38" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L38" s="197">
+      <c r="L38" s="139">
         <v>31</v>
       </c>
-      <c r="M38" s="200" t="s">
+      <c r="M38" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N38" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O38" s="199" t="s">
+      <c r="O38" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P38" s="200" t="s">
+      <c r="P38" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q38" s="208" t="s">
+      <c r="Q38" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R38" s="14">
@@ -35136,10 +35650,10 @@
       <c r="K39" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L39" s="197">
+      <c r="L39" s="139">
         <v>32</v>
       </c>
-      <c r="M39" s="200" t="s">
+      <c r="M39" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N39" s="18" t="s">
@@ -35148,10 +35662,10 @@
       <c r="O39" s="18" t="s">
         <v>672</v>
       </c>
-      <c r="P39" s="200" t="s">
+      <c r="P39" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q39" s="208" t="s">
+      <c r="Q39" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R39" s="14">
@@ -35193,22 +35707,22 @@
       <c r="K40" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L40" s="197">
+      <c r="L40" s="139">
         <v>29</v>
       </c>
-      <c r="M40" s="200" t="s">
+      <c r="M40" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N40" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O40" s="199" t="s">
+      <c r="O40" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P40" s="200" t="s">
+      <c r="P40" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q40" s="208" t="s">
+      <c r="Q40" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R40" s="14">
@@ -35250,10 +35764,10 @@
       <c r="K41" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L41" s="197">
+      <c r="L41" s="139">
         <v>27</v>
       </c>
-      <c r="M41" s="200" t="s">
+      <c r="M41" s="141" t="s">
         <v>688</v>
       </c>
       <c r="N41" s="18" t="s">
@@ -35262,10 +35776,10 @@
       <c r="O41" s="18" t="s">
         <v>673</v>
       </c>
-      <c r="P41" s="200" t="s">
+      <c r="P41" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q41" s="208" t="s">
+      <c r="Q41" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R41" s="14">
@@ -35307,10 +35821,10 @@
       <c r="K42" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L42" s="197">
+      <c r="L42" s="139">
         <v>28</v>
       </c>
-      <c r="M42" s="200" t="s">
+      <c r="M42" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N42" s="18" t="s">
@@ -35319,10 +35833,10 @@
       <c r="O42" s="18" t="s">
         <v>674</v>
       </c>
-      <c r="P42" s="200" t="s">
+      <c r="P42" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q42" s="208" t="s">
+      <c r="Q42" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R42" s="14">
@@ -35364,10 +35878,10 @@
       <c r="K43" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L43" s="197">
+      <c r="L43" s="139">
         <v>26</v>
       </c>
-      <c r="M43" s="200" t="s">
+      <c r="M43" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N43" s="18" t="s">
@@ -35376,10 +35890,10 @@
       <c r="O43" s="18" t="s">
         <v>675</v>
       </c>
-      <c r="P43" s="200" t="s">
+      <c r="P43" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q43" s="208" t="s">
+      <c r="Q43" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R43" s="14">
@@ -35419,10 +35933,10 @@
       <c r="K44" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L44" s="197">
+      <c r="L44" s="139">
         <v>23</v>
       </c>
-      <c r="M44" s="200" t="s">
+      <c r="M44" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N44" s="18" t="s">
@@ -35431,10 +35945,10 @@
       <c r="O44" s="18" t="s">
         <v>676</v>
       </c>
-      <c r="P44" s="200" t="s">
+      <c r="P44" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q44" s="208" t="s">
+      <c r="Q44" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R44" s="14">
@@ -35466,35 +35980,35 @@
         <v>61</v>
       </c>
       <c r="I45" s="13"/>
-      <c r="J45" s="217">
+      <c r="J45" s="151">
         <v>39</v>
       </c>
-      <c r="K45" s="213" t="s">
+      <c r="K45" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="L45" s="214" t="s">
+      <c r="L45" s="148" t="s">
         <v>74</v>
       </c>
-      <c r="M45" s="213" t="s">
+      <c r="M45" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="N45" s="213" t="s">
+      <c r="N45" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="O45" s="215" t="s">
+      <c r="O45" s="149" t="s">
         <v>74</v>
       </c>
-      <c r="P45" s="216" t="s">
+      <c r="P45" s="150" t="s">
         <v>659</v>
       </c>
-      <c r="Q45" s="215"/>
-      <c r="R45" s="217">
+      <c r="Q45" s="149"/>
+      <c r="R45" s="151">
         <v>39</v>
       </c>
-      <c r="S45" s="213" t="s">
+      <c r="S45" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="T45" s="213" t="s">
+      <c r="T45" s="147" t="s">
         <v>660</v>
       </c>
       <c r="V45" s="9" t="str">
@@ -35524,26 +36038,26 @@
       <c r="J46" s="14">
         <v>40</v>
       </c>
-      <c r="K46" s="209" t="s">
+      <c r="K46" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L46" s="210"/>
-      <c r="M46" s="211"/>
-      <c r="N46" s="209" t="s">
+      <c r="L46" s="139"/>
+      <c r="M46" s="141"/>
+      <c r="N46" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O46" s="209"/>
-      <c r="P46" s="211" t="s">
+      <c r="O46" s="18"/>
+      <c r="P46" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q46" s="212"/>
+      <c r="Q46" s="140"/>
       <c r="R46" s="14">
         <v>40</v>
       </c>
-      <c r="S46" s="209" t="s">
+      <c r="S46" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="T46" s="209" t="s">
+      <c r="T46" s="18" t="s">
         <v>270</v>
       </c>
       <c r="V46" s="9" t="str">
@@ -35566,35 +36080,35 @@
         <v>64</v>
       </c>
       <c r="I47" s="13"/>
-      <c r="J47" s="217">
+      <c r="J47" s="151">
         <v>41</v>
       </c>
-      <c r="K47" s="213" t="s">
+      <c r="K47" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="L47" s="214" t="s">
+      <c r="L47" s="148" t="s">
         <v>74</v>
       </c>
-      <c r="M47" s="213" t="s">
+      <c r="M47" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="N47" s="213" t="s">
+      <c r="N47" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="O47" s="215" t="s">
+      <c r="O47" s="149" t="s">
         <v>74</v>
       </c>
-      <c r="P47" s="216" t="s">
+      <c r="P47" s="150" t="s">
         <v>659</v>
       </c>
-      <c r="Q47" s="215"/>
-      <c r="R47" s="217">
+      <c r="Q47" s="149"/>
+      <c r="R47" s="151">
         <v>41</v>
       </c>
-      <c r="S47" s="213" t="s">
+      <c r="S47" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="T47" s="213" t="s">
+      <c r="T47" s="147" t="s">
         <v>660</v>
       </c>
       <c r="V47" s="9" t="str">
@@ -35624,26 +36138,26 @@
       <c r="J48" s="14">
         <v>42</v>
       </c>
-      <c r="K48" s="209" t="s">
+      <c r="K48" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L48" s="210"/>
-      <c r="M48" s="211"/>
-      <c r="N48" s="209" t="s">
+      <c r="L48" s="139"/>
+      <c r="M48" s="141"/>
+      <c r="N48" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O48" s="209"/>
-      <c r="P48" s="211" t="s">
+      <c r="O48" s="18"/>
+      <c r="P48" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q48" s="212"/>
+      <c r="Q48" s="140"/>
       <c r="R48" s="14">
         <v>42</v>
       </c>
-      <c r="S48" s="209" t="s">
+      <c r="S48" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="T48" s="209" t="s">
+      <c r="T48" s="18" t="s">
         <v>271</v>
       </c>
       <c r="V48" s="9" t="str">
@@ -35676,20 +36190,20 @@
       <c r="K49" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="L49" s="197">
+      <c r="L49" s="139">
         <v>2</v>
       </c>
-      <c r="M49" s="200"/>
+      <c r="M49" s="141"/>
       <c r="N49" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="O49" s="206" t="s">
+      <c r="O49" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P49" s="200" t="s">
+      <c r="P49" s="141" t="s">
         <v>658</v>
       </c>
-      <c r="Q49" s="199"/>
+      <c r="Q49" s="140"/>
       <c r="R49" s="14">
         <v>43</v>
       </c>
@@ -35729,20 +36243,20 @@
       <c r="K50" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L50" s="197" t="s">
+      <c r="L50" s="139" t="s">
         <v>164</v>
       </c>
-      <c r="M50" s="200"/>
+      <c r="M50" s="141"/>
       <c r="N50" s="18" t="s">
         <v>169</v>
       </c>
       <c r="O50" s="18" t="s">
         <v>677</v>
       </c>
-      <c r="P50" s="200" t="s">
+      <c r="P50" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q50" s="208" t="s">
+      <c r="Q50" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R50" s="14">
@@ -35782,20 +36296,20 @@
       <c r="K51" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="L51" s="197">
+      <c r="L51" s="139">
         <v>2</v>
       </c>
-      <c r="M51" s="200"/>
+      <c r="M51" s="141"/>
       <c r="N51" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="O51" s="206" t="s">
+      <c r="O51" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P51" s="200" t="s">
+      <c r="P51" s="141" t="s">
         <v>658</v>
       </c>
-      <c r="Q51" s="199"/>
+      <c r="Q51" s="140"/>
       <c r="R51" s="14">
         <v>45</v>
       </c>
@@ -35835,10 +36349,10 @@
       <c r="K52" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L52" s="197">
+      <c r="L52" s="139">
         <v>24</v>
       </c>
-      <c r="M52" s="200" t="s">
+      <c r="M52" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N52" s="18" t="s">
@@ -35847,10 +36361,10 @@
       <c r="O52" s="18" t="s">
         <v>678</v>
       </c>
-      <c r="P52" s="200" t="s">
+      <c r="P52" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q52" s="208" t="s">
+      <c r="Q52" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R52" s="14">
@@ -35892,22 +36406,22 @@
       <c r="K53" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L53" s="197">
+      <c r="L53" s="139">
         <v>22</v>
       </c>
-      <c r="M53" s="200" t="s">
+      <c r="M53" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N53" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O53" s="199" t="s">
+      <c r="O53" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P53" s="200" t="s">
+      <c r="P53" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q53" s="208" t="s">
+      <c r="Q53" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R53" s="14">
@@ -35947,22 +36461,22 @@
       <c r="K54" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L54" s="197">
+      <c r="L54" s="139">
         <v>18</v>
       </c>
-      <c r="M54" s="200" t="s">
+      <c r="M54" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N54" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O54" s="199" t="s">
+      <c r="O54" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P54" s="200" t="s">
+      <c r="P54" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q54" s="208" t="s">
+      <c r="Q54" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R54" s="14">
@@ -36004,22 +36518,22 @@
       <c r="K55" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L55" s="197">
+      <c r="L55" s="139">
         <v>15</v>
       </c>
-      <c r="M55" s="200" t="s">
+      <c r="M55" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N55" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O55" s="199" t="s">
+      <c r="O55" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P55" s="200" t="s">
+      <c r="P55" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q55" s="208" t="s">
+      <c r="Q55" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R55" s="14">
@@ -36061,22 +36575,22 @@
       <c r="K56" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L56" s="197">
+      <c r="L56" s="139">
         <v>16</v>
       </c>
-      <c r="M56" s="200" t="s">
+      <c r="M56" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N56" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O56" s="199" t="s">
+      <c r="O56" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P56" s="200" t="s">
+      <c r="P56" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q56" s="208" t="s">
+      <c r="Q56" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R56" s="14">
@@ -36116,22 +36630,22 @@
       <c r="K57" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="L57" s="197">
+      <c r="L57" s="139">
         <v>4</v>
       </c>
-      <c r="M57" s="200" t="s">
+      <c r="M57" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N57" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="O57" s="199" t="s">
+      <c r="O57" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P57" s="200" t="s">
+      <c r="P57" s="141" t="s">
         <v>658</v>
       </c>
-      <c r="Q57" s="199"/>
+      <c r="Q57" s="140"/>
       <c r="R57" s="14">
         <v>51</v>
       </c>
@@ -36171,22 +36685,22 @@
       <c r="K58" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L58" s="197">
+      <c r="L58" s="139">
         <v>13</v>
       </c>
-      <c r="M58" s="200" t="s">
+      <c r="M58" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N58" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O58" s="199" t="s">
+      <c r="O58" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P58" s="200" t="s">
+      <c r="P58" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q58" s="208" t="s">
+      <c r="Q58" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R58" s="14">
@@ -36228,22 +36742,22 @@
       <c r="K59" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L59" s="197">
+      <c r="L59" s="139">
         <v>11</v>
       </c>
-      <c r="M59" s="200" t="s">
+      <c r="M59" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N59" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="O59" s="199" t="s">
+      <c r="O59" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P59" s="200" t="s">
+      <c r="P59" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q59" s="208" t="s">
+      <c r="Q59" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R59" s="14">
@@ -36285,10 +36799,10 @@
       <c r="K60" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L60" s="197">
+      <c r="L60" s="139">
         <v>12</v>
       </c>
-      <c r="M60" s="200" t="s">
+      <c r="M60" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N60" s="18" t="s">
@@ -36297,10 +36811,10 @@
       <c r="O60" s="18" t="s">
         <v>679</v>
       </c>
-      <c r="P60" s="200" t="s">
+      <c r="P60" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q60" s="208" t="s">
+      <c r="Q60" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R60" s="14">
@@ -36342,10 +36856,10 @@
       <c r="K61" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L61" s="197">
+      <c r="L61" s="139">
         <v>10</v>
       </c>
-      <c r="M61" s="200" t="s">
+      <c r="M61" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N61" s="18" t="s">
@@ -36354,10 +36868,10 @@
       <c r="O61" s="18" t="s">
         <v>680</v>
       </c>
-      <c r="P61" s="200" t="s">
+      <c r="P61" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q61" s="208" t="s">
+      <c r="Q61" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R61" s="14">
@@ -36399,22 +36913,22 @@
       <c r="K62" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="L62" s="197">
+      <c r="L62" s="139">
         <v>5</v>
       </c>
-      <c r="M62" s="200" t="s">
+      <c r="M62" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N62" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="O62" s="199" t="s">
+      <c r="O62" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="P62" s="200" t="s">
+      <c r="P62" s="141" t="s">
         <v>658</v>
       </c>
-      <c r="Q62" s="208" t="s">
+      <c r="Q62" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R62" s="14">
@@ -36446,35 +36960,35 @@
         <v>62</v>
       </c>
       <c r="I63" s="13"/>
-      <c r="J63" s="217">
+      <c r="J63" s="151">
         <v>57</v>
       </c>
-      <c r="K63" s="213" t="s">
+      <c r="K63" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="L63" s="214" t="s">
+      <c r="L63" s="148" t="s">
         <v>74</v>
       </c>
-      <c r="M63" s="213" t="s">
+      <c r="M63" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="N63" s="213" t="s">
+      <c r="N63" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="O63" s="215" t="s">
+      <c r="O63" s="149" t="s">
         <v>74</v>
       </c>
-      <c r="P63" s="216" t="s">
+      <c r="P63" s="150" t="s">
         <v>659</v>
       </c>
-      <c r="Q63" s="215"/>
-      <c r="R63" s="217">
+      <c r="Q63" s="149"/>
+      <c r="R63" s="151">
         <v>57</v>
       </c>
-      <c r="S63" s="213" t="s">
+      <c r="S63" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="T63" s="213" t="s">
+      <c r="T63" s="147" t="s">
         <v>660</v>
       </c>
       <c r="V63" s="9" t="str">
@@ -36507,20 +37021,20 @@
       <c r="K64" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="L64" s="197">
+      <c r="L64" s="139">
         <v>8</v>
       </c>
-      <c r="M64" s="200"/>
+      <c r="M64" s="141"/>
       <c r="N64" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="O64" s="206" t="s">
+      <c r="O64" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P64" s="200" t="s">
+      <c r="P64" s="141" t="s">
         <v>658</v>
       </c>
-      <c r="Q64" s="208" t="s">
+      <c r="Q64" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R64" s="14">
@@ -36562,10 +37076,10 @@
       <c r="K65" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L65" s="197">
+      <c r="L65" s="139">
         <v>8</v>
       </c>
-      <c r="M65" s="200" t="s">
+      <c r="M65" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N65" s="18" t="s">
@@ -36574,10 +37088,10 @@
       <c r="O65" s="18" t="s">
         <v>681</v>
       </c>
-      <c r="P65" s="200" t="s">
+      <c r="P65" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q65" s="208" t="s">
+      <c r="Q65" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R65" s="14">
@@ -36619,10 +37133,10 @@
       <c r="K66" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L66" s="197">
+      <c r="L66" s="139">
         <v>7</v>
       </c>
-      <c r="M66" s="200" t="s">
+      <c r="M66" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N66" s="18" t="s">
@@ -36631,10 +37145,10 @@
       <c r="O66" s="18" t="s">
         <v>682</v>
       </c>
-      <c r="P66" s="200" t="s">
+      <c r="P66" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q66" s="208" t="s">
+      <c r="Q66" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R66" s="14">
@@ -36676,10 +37190,10 @@
       <c r="K67" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L67" s="197">
+      <c r="L67" s="139">
         <v>5</v>
       </c>
-      <c r="M67" s="200" t="s">
+      <c r="M67" s="141" t="s">
         <v>657</v>
       </c>
       <c r="N67" s="18" t="s">
@@ -36688,10 +37202,10 @@
       <c r="O67" s="18" t="s">
         <v>683</v>
       </c>
-      <c r="P67" s="200" t="s">
+      <c r="P67" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q67" s="208" t="s">
+      <c r="Q67" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R67" s="14">
@@ -36730,22 +37244,22 @@
       <c r="K68" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="L68" s="197" t="s">
+      <c r="L68" s="139" t="s">
         <v>74</v>
       </c>
-      <c r="M68" s="200" t="s">
+      <c r="M68" s="141" t="s">
         <v>658</v>
       </c>
       <c r="N68" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="O68" s="206" t="s">
+      <c r="O68" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P68" s="200" t="s">
+      <c r="P68" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q68" s="199"/>
+      <c r="Q68" s="140"/>
       <c r="R68" s="14">
         <v>62</v>
       </c>
@@ -36785,10 +37299,10 @@
       <c r="K69" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="L69" s="197">
+      <c r="L69" s="139">
         <v>3</v>
       </c>
-      <c r="M69" s="200" t="s">
+      <c r="M69" s="141" t="s">
         <v>688</v>
       </c>
       <c r="N69" s="18" t="s">
@@ -36797,10 +37311,10 @@
       <c r="O69" s="18" t="s">
         <v>684</v>
       </c>
-      <c r="P69" s="200" t="s">
+      <c r="P69" s="141" t="s">
         <v>657</v>
       </c>
-      <c r="Q69" s="208" t="s">
+      <c r="Q69" s="140" t="s">
         <v>686</v>
       </c>
       <c r="R69" s="14">
@@ -36842,20 +37356,20 @@
       <c r="K70" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="L70" s="197">
+      <c r="L70" s="139">
         <v>9</v>
       </c>
-      <c r="M70" s="200"/>
+      <c r="M70" s="141"/>
       <c r="N70" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="O70" s="206" t="s">
+      <c r="O70" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="P70" s="200" t="s">
+      <c r="P70" s="141" t="s">
         <v>658</v>
       </c>
-      <c r="Q70" s="199"/>
+      <c r="Q70" s="140"/>
       <c r="R70" s="14">
         <v>64</v>
       </c>

--- a/doc/notes/ro-rl78-maxv-learning.xlsx
+++ b/doc/notes/ro-rl78-maxv-learning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\0_forge\ro-rl78-maxv-learning\doc\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845FE8D0-A19B-4EF7-AF4D-F3D9E9B2953E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CC9C05-EBED-40B3-88DE-97FAF23E96F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-225" windowWidth="29040" windowHeight="16440" firstSheet="4" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="ROM" sheetId="25" r:id="rId17"/>
     <sheet name="FLOW" sheetId="26" r:id="rId18"/>
     <sheet name="DMA" sheetId="27" r:id="rId19"/>
+    <sheet name="BiUART" sheetId="29" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4'!$A$6:$AB$70</definedName>
@@ -8587,6 +8588,1291 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="130" name="テキスト ボックス 129">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEEBBD13-853F-41AE-8D2E-8A3738D43A45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4000500" y="3619500"/>
+          <a:ext cx="762000" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>USB-UART</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="30000"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="131" name="直線矢印コネクタ 130">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{121FCA77-CB7E-4BE0-8469-B54DD61CDF6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5524500" y="2476500"/>
+          <a:ext cx="0" cy="1524000"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="oval"/>
+          <a:tailEnd type="none"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>184547</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>5953</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="133" name="直線矢印コネクタ 132">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77DBE3D7-EA3F-F320-02C6-70B16D8B9415}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3042047" y="4191000"/>
+          <a:ext cx="958453" cy="5953"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="134" name="テキスト ボックス 133">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D3C0345-9D52-E837-C1A3-7279387BB5EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2286000" y="3619500"/>
+          <a:ext cx="762000" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>PC</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="30000"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="136" name="直線矢印コネクタ 135">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBFCBB62-3922-61EC-E3E6-B715CED46BB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4762500" y="4000500"/>
+          <a:ext cx="2095500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="138" name="テキスト ボックス 137">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89A400C0-5F2B-CFB9-4518-53D19A02F36F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4572000" y="3810000"/>
+          <a:ext cx="190500" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="800"/>
+            <a:t>TX</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="139" name="直線矢印コネクタ 138">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93D701ED-EB74-4806-FBC0-BAFB91FC1436}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4762500" y="4381500"/>
+          <a:ext cx="2095500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="140" name="テキスト ボックス 139">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34E8E89F-B4D4-67AE-FE3F-256230BA6388}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4572000" y="4191000"/>
+          <a:ext cx="190500" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="800"/>
+            <a:t>RX</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="141" name="テキスト ボックス 140">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{300EB7AF-78BA-3E8F-9CBF-AD3A6EC9F869}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6858000" y="3619500"/>
+          <a:ext cx="762000" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>MCU</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="30000"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="145" name="テキスト ボックス 144">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D3CDDC0-B964-035C-E0DE-FBDE0A538346}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6858000" y="3810000"/>
+          <a:ext cx="190500" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="800"/>
+            <a:t>RX</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="146" name="テキスト ボックス 145">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1B1517A-68FB-BE29-F022-B5E054094D43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6858000" y="4191000"/>
+          <a:ext cx="762000" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="800"/>
+            <a:t>  TX (Open</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="800" baseline="0"/>
+            <a:t> Drain)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="147" name="テキスト ボックス 146">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71240E68-2482-76A5-FF2A-FA2C8FF8CD3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6858000" y="2095500"/>
+          <a:ext cx="762000" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>CPLD/FPGA</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="30000"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="148" name="直線矢印コネクタ 147">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC7088DD-C215-D7B3-53DC-32CEED6F4F1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7239000" y="3048000"/>
+          <a:ext cx="0" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="triangle"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="151" name="テキスト ボックス 150">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5039324D-660E-ED19-7429-1C4E90AB9FAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7239000" y="3238500"/>
+          <a:ext cx="381000" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="800"/>
+            <a:t>JTAG</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="152" name="テキスト ボックス 151">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48084D97-395A-1B3B-56B6-7FDE487CC651}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6858000" y="2286000"/>
+          <a:ext cx="571500" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="800"/>
+            <a:t>  RX</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="800" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="800" baseline="0"/>
+            <a:t>(input)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="153" name="テキスト ボックス 152">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EE80F22-70E2-3491-507C-054739C85B5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6858000" y="2667000"/>
+          <a:ext cx="762000" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="800"/>
+            <a:t>  TX (output)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="154" name="直線矢印コネクタ 153">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D6B0105-8877-EC20-ECDF-EDD6C5A5F05B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5524500" y="2476500"/>
+          <a:ext cx="1333500" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="158" name="直線矢印コネクタ 157">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EC55C19-2C9E-C57D-D3A7-1EA68B2981A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6096000" y="2857500"/>
+          <a:ext cx="0" cy="1524000"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>125016</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>65483</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>71438</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>5952</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="132" name="テキスト ボックス 131">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97D3A0BD-113E-4B7E-93C9-413474E864A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="5938242" y="3205757"/>
+          <a:ext cx="321469" cy="136922"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="800"/>
+            <a:t>1k</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="800"/>
+            <a:t>Ω</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="161" name="直線矢印コネクタ 160">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19EA6F74-B291-5D0B-D732-D19853C7FF69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="6096000" y="2857500"/>
+          <a:ext cx="762000" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="none"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -33179,6 +34465,16 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29E5D87-F4F7-449C-A476-A67CED2034FA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="2.85546875" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A881EA-E0AB-4311-93A9-080EF2A17ED8}">
   <dimension ref="B2:C4"/>

--- a/doc/notes/ro-rl78-maxv-learning.xlsx
+++ b/doc/notes/ro-rl78-maxv-learning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\0_forge\ro-rl78-maxv-learning\doc\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CC9C05-EBED-40B3-88DE-97FAF23E96F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3F4314-C066-40AF-A4B1-7FAF77304B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-225" windowWidth="29040" windowHeight="16440" firstSheet="4" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="754">
   <si>
     <t>Block Diagram</t>
   </si>
@@ -2867,6 +2867,18 @@
       </rPr>
       <t>(DST0)</t>
     </r>
+  </si>
+  <si>
+    <t>TCK Count *1</t>
+  </si>
+  <si>
+    <t>*1</t>
+  </si>
+  <si>
+    <t>Reducing the scan length field to one byte would save at most approximately 0.23 seconds, less than 10% of the total execution time.</t>
+  </si>
+  <si>
+    <t>The 32-bit length field will therefore be retained to preserve protocol compatibility and support longer SVF scan operations in the future.</t>
   </si>
 </sst>
 </file>
@@ -4509,6 +4521,15 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -4527,13 +4548,97 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="25" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="53" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="24" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="25" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="67" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4557,94 +4662,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="16" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="64" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="66" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="63" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="70" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="71" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="53" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="60" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="62" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="61" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="69" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4658,15 +4679,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -25576,11 +25588,11 @@
       <c r="H4" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="J4" s="165" t="s">
+      <c r="J4" s="168" t="s">
         <v>664</v>
       </c>
-      <c r="K4" s="165"/>
-      <c r="L4" s="165"/>
+      <c r="K4" s="168"/>
+      <c r="L4" s="168"/>
     </row>
     <row r="5" spans="2:12">
       <c r="B5" s="14">
@@ -27956,32 +27968,32 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:20">
-      <c r="B4" s="169"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="169" t="s">
+      <c r="B4" s="172"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="172" t="s">
         <v>442</v>
       </c>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="169"/>
-      <c r="I4" s="169"/>
-      <c r="J4" s="169"/>
-      <c r="K4" s="169"/>
-      <c r="L4" s="169"/>
-      <c r="M4" s="169"/>
-      <c r="N4" s="169"/>
-      <c r="O4" s="169"/>
-      <c r="P4" s="169"/>
-      <c r="Q4" s="169"/>
-      <c r="R4" s="169"/>
-      <c r="S4" s="169"/>
-      <c r="T4" s="169"/>
+      <c r="F4" s="172"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="172"/>
+      <c r="I4" s="172"/>
+      <c r="J4" s="172"/>
+      <c r="K4" s="172"/>
+      <c r="L4" s="172"/>
+      <c r="M4" s="172"/>
+      <c r="N4" s="172"/>
+      <c r="O4" s="172"/>
+      <c r="P4" s="172"/>
+      <c r="Q4" s="172"/>
+      <c r="R4" s="172"/>
+      <c r="S4" s="172"/>
+      <c r="T4" s="172"/>
     </row>
     <row r="5" spans="2:20">
-      <c r="B5" s="169"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="169"/>
+      <c r="B5" s="172"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="172"/>
       <c r="E5" s="44">
         <v>0</v>
       </c>
@@ -28032,9 +28044,9 @@
       </c>
     </row>
     <row r="6" spans="2:20" ht="103.5" customHeight="1">
-      <c r="B6" s="169"/>
-      <c r="C6" s="169"/>
-      <c r="D6" s="169"/>
+      <c r="B6" s="172"/>
+      <c r="C6" s="172"/>
+      <c r="D6" s="172"/>
       <c r="E6" s="63" t="s">
         <v>440</v>
       </c>
@@ -28085,7 +28097,7 @@
       </c>
     </row>
     <row r="7" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B7" s="166" t="s">
+      <c r="B7" s="169" t="s">
         <v>441</v>
       </c>
       <c r="C7" s="44">
@@ -28144,7 +28156,7 @@
       </c>
     </row>
     <row r="8" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B8" s="167"/>
+      <c r="B8" s="170"/>
       <c r="C8" s="44">
         <v>1</v>
       </c>
@@ -28201,7 +28213,7 @@
       </c>
     </row>
     <row r="9" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B9" s="167"/>
+      <c r="B9" s="170"/>
       <c r="C9" s="44">
         <v>2</v>
       </c>
@@ -28258,7 +28270,7 @@
       </c>
     </row>
     <row r="10" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B10" s="167"/>
+      <c r="B10" s="170"/>
       <c r="C10" s="44">
         <v>3</v>
       </c>
@@ -28315,7 +28327,7 @@
       </c>
     </row>
     <row r="11" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B11" s="167"/>
+      <c r="B11" s="170"/>
       <c r="C11" s="44">
         <v>4</v>
       </c>
@@ -28372,7 +28384,7 @@
       </c>
     </row>
     <row r="12" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B12" s="167"/>
+      <c r="B12" s="170"/>
       <c r="C12" s="44">
         <v>5</v>
       </c>
@@ -28429,7 +28441,7 @@
       </c>
     </row>
     <row r="13" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B13" s="167"/>
+      <c r="B13" s="170"/>
       <c r="C13" s="44">
         <v>6</v>
       </c>
@@ -28486,7 +28498,7 @@
       </c>
     </row>
     <row r="14" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B14" s="167"/>
+      <c r="B14" s="170"/>
       <c r="C14" s="44">
         <v>7</v>
       </c>
@@ -28543,7 +28555,7 @@
       </c>
     </row>
     <row r="15" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B15" s="167"/>
+      <c r="B15" s="170"/>
       <c r="C15" s="44">
         <v>8</v>
       </c>
@@ -28600,7 +28612,7 @@
       </c>
     </row>
     <row r="16" spans="2:20" ht="31.5" customHeight="1">
-      <c r="B16" s="167"/>
+      <c r="B16" s="170"/>
       <c r="C16" s="44">
         <v>9</v>
       </c>
@@ -28657,7 +28669,7 @@
       </c>
     </row>
     <row r="17" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B17" s="167"/>
+      <c r="B17" s="170"/>
       <c r="C17" s="44">
         <v>10</v>
       </c>
@@ -28714,7 +28726,7 @@
       </c>
     </row>
     <row r="18" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B18" s="167"/>
+      <c r="B18" s="170"/>
       <c r="C18" s="44">
         <v>11</v>
       </c>
@@ -28771,7 +28783,7 @@
       </c>
     </row>
     <row r="19" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B19" s="167"/>
+      <c r="B19" s="170"/>
       <c r="C19" s="44">
         <v>12</v>
       </c>
@@ -28828,7 +28840,7 @@
       </c>
     </row>
     <row r="20" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B20" s="167"/>
+      <c r="B20" s="170"/>
       <c r="C20" s="44">
         <v>13</v>
       </c>
@@ -28885,7 +28897,7 @@
       </c>
     </row>
     <row r="21" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B21" s="167"/>
+      <c r="B21" s="170"/>
       <c r="C21" s="44">
         <v>14</v>
       </c>
@@ -28944,7 +28956,7 @@
       <c r="V21" s="39"/>
     </row>
     <row r="22" spans="2:22" ht="31.5" customHeight="1">
-      <c r="B22" s="168"/>
+      <c r="B22" s="171"/>
       <c r="C22" s="44">
         <v>15</v>
       </c>
@@ -31950,7 +31962,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F837E406-9569-443C-823E-A0F068C6235A}">
-  <dimension ref="B2:P40"/>
+  <dimension ref="B2:P44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="38" customWidth="1"/>
@@ -31973,34 +31985,34 @@
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="191" t="s">
+      <c r="B3" s="196" t="s">
         <v>489</v>
       </c>
-      <c r="C3" s="204" t="s">
+      <c r="C3" s="191" t="s">
         <v>488</v>
       </c>
-      <c r="D3" s="202"/>
-      <c r="E3" s="202"/>
-      <c r="F3" s="202"/>
-      <c r="G3" s="202"/>
-      <c r="H3" s="205"/>
-      <c r="I3" s="201" t="s">
+      <c r="D3" s="189"/>
+      <c r="E3" s="189"/>
+      <c r="F3" s="189"/>
+      <c r="G3" s="189"/>
+      <c r="H3" s="192"/>
+      <c r="I3" s="188" t="s">
         <v>487</v>
       </c>
-      <c r="J3" s="202"/>
-      <c r="K3" s="202"/>
-      <c r="L3" s="202"/>
-      <c r="M3" s="202"/>
-      <c r="N3" s="203"/>
+      <c r="J3" s="189"/>
+      <c r="K3" s="189"/>
+      <c r="L3" s="189"/>
+      <c r="M3" s="189"/>
+      <c r="N3" s="190"/>
       <c r="O3" s="104" t="s">
         <v>486</v>
       </c>
-      <c r="P3" s="197" t="s">
+      <c r="P3" s="185" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B4" s="192"/>
+      <c r="B4" s="197"/>
       <c r="C4" s="105" t="s">
         <v>373</v>
       </c>
@@ -32040,7 +32052,7 @@
       <c r="O4" s="110" t="s">
         <v>479</v>
       </c>
-      <c r="P4" s="198"/>
+      <c r="P4" s="186"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickTop="1">
       <c r="B5" s="64" t="s">
@@ -32116,12 +32128,12 @@
         <f t="shared" si="0"/>
         <v>0x01</v>
       </c>
-      <c r="J6" s="199" t="s">
+      <c r="J6" s="176" t="s">
         <v>508</v>
       </c>
-      <c r="K6" s="199"/>
-      <c r="L6" s="199"/>
-      <c r="M6" s="199"/>
+      <c r="K6" s="176"/>
+      <c r="L6" s="176"/>
+      <c r="M6" s="176"/>
       <c r="N6" s="77" t="s">
         <v>492</v>
       </c>
@@ -32158,12 +32170,12 @@
         <f t="shared" si="0"/>
         <v>0x02</v>
       </c>
-      <c r="J7" s="199" t="s">
+      <c r="J7" s="176" t="s">
         <v>523</v>
       </c>
-      <c r="K7" s="199"/>
-      <c r="L7" s="199"/>
-      <c r="M7" s="199"/>
+      <c r="K7" s="176"/>
+      <c r="L7" s="176"/>
+      <c r="M7" s="176"/>
       <c r="N7" s="77" t="s">
         <v>492</v>
       </c>
@@ -32200,12 +32212,12 @@
         <f t="shared" si="0"/>
         <v>0x03</v>
       </c>
-      <c r="J8" s="199" t="s">
+      <c r="J8" s="176" t="s">
         <v>506</v>
       </c>
-      <c r="K8" s="199"/>
-      <c r="L8" s="199"/>
-      <c r="M8" s="199"/>
+      <c r="K8" s="176"/>
+      <c r="L8" s="176"/>
+      <c r="M8" s="176"/>
       <c r="N8" s="77" t="s">
         <v>492</v>
       </c>
@@ -32242,14 +32254,14 @@
         <f t="shared" si="0"/>
         <v>0x04</v>
       </c>
-      <c r="J9" s="199" t="s">
+      <c r="J9" s="176" t="s">
         <v>503</v>
       </c>
-      <c r="K9" s="199"/>
-      <c r="L9" s="199" t="s">
+      <c r="K9" s="176"/>
+      <c r="L9" s="176" t="s">
         <v>502</v>
       </c>
-      <c r="M9" s="199"/>
+      <c r="M9" s="176"/>
       <c r="N9" s="77" t="s">
         <v>492</v>
       </c>
@@ -32411,12 +32423,12 @@
       <c r="C13" s="73" t="s">
         <v>564</v>
       </c>
-      <c r="D13" s="200" t="s">
+      <c r="D13" s="187" t="s">
         <v>508</v>
       </c>
-      <c r="E13" s="200"/>
-      <c r="F13" s="200"/>
-      <c r="G13" s="200"/>
+      <c r="E13" s="187"/>
+      <c r="F13" s="187"/>
+      <c r="G13" s="187"/>
       <c r="H13" s="103" t="s">
         <v>492</v>
       </c>
@@ -32501,12 +32513,12 @@
       <c r="C15" s="73" t="s">
         <v>566</v>
       </c>
-      <c r="D15" s="199" t="s">
+      <c r="D15" s="176" t="s">
         <v>506</v>
       </c>
-      <c r="E15" s="199"/>
-      <c r="F15" s="199"/>
-      <c r="G15" s="199"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
+      <c r="G15" s="176"/>
       <c r="H15" s="75" t="s">
         <v>492</v>
       </c>
@@ -32543,14 +32555,14 @@
       <c r="C16" s="73" t="s">
         <v>567</v>
       </c>
-      <c r="D16" s="199" t="s">
+      <c r="D16" s="176" t="s">
         <v>503</v>
       </c>
-      <c r="E16" s="199"/>
-      <c r="F16" s="199" t="s">
+      <c r="E16" s="176"/>
+      <c r="F16" s="176" t="s">
         <v>502</v>
       </c>
-      <c r="G16" s="199"/>
+      <c r="G16" s="176"/>
       <c r="H16" s="75" t="s">
         <v>492</v>
       </c>
@@ -32732,34 +32744,34 @@
       <c r="D21" s="58"/>
     </row>
     <row r="22" spans="2:16">
-      <c r="B22" s="193" t="s">
+      <c r="B22" s="198" t="s">
         <v>489</v>
       </c>
-      <c r="C22" s="176" t="s">
+      <c r="C22" s="207" t="s">
         <v>488</v>
       </c>
-      <c r="D22" s="177"/>
-      <c r="E22" s="177"/>
-      <c r="F22" s="177"/>
-      <c r="G22" s="177"/>
-      <c r="H22" s="177"/>
-      <c r="I22" s="177"/>
-      <c r="J22" s="178"/>
-      <c r="K22" s="176" t="s">
+      <c r="D22" s="208"/>
+      <c r="E22" s="208"/>
+      <c r="F22" s="208"/>
+      <c r="G22" s="208"/>
+      <c r="H22" s="208"/>
+      <c r="I22" s="208"/>
+      <c r="J22" s="209"/>
+      <c r="K22" s="207" t="s">
         <v>487</v>
       </c>
-      <c r="L22" s="177"/>
-      <c r="M22" s="177"/>
-      <c r="N22" s="178"/>
+      <c r="L22" s="208"/>
+      <c r="M22" s="208"/>
+      <c r="N22" s="209"/>
       <c r="O22" s="104" t="s">
         <v>486</v>
       </c>
-      <c r="P22" s="206" t="s">
+      <c r="P22" s="173" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B23" s="194"/>
+      <c r="B23" s="199"/>
       <c r="C23" s="111" t="s">
         <v>373</v>
       </c>
@@ -32775,21 +32787,21 @@
       <c r="G23" s="113" t="s">
         <v>482</v>
       </c>
-      <c r="H23" s="208" t="s">
+      <c r="H23" s="177" t="s">
         <v>481</v>
       </c>
-      <c r="I23" s="180"/>
-      <c r="J23" s="181"/>
-      <c r="K23" s="179" t="s">
+      <c r="I23" s="178"/>
+      <c r="J23" s="179"/>
+      <c r="K23" s="210" t="s">
         <v>480</v>
       </c>
-      <c r="L23" s="180"/>
-      <c r="M23" s="180"/>
-      <c r="N23" s="181"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="178"/>
+      <c r="N23" s="179"/>
       <c r="O23" s="110" t="s">
         <v>479</v>
       </c>
-      <c r="P23" s="207"/>
+      <c r="P23" s="174"/>
     </row>
     <row r="24" spans="2:16" ht="15.75" thickTop="1">
       <c r="B24" s="98" t="s">
@@ -32810,17 +32822,17 @@
       <c r="G24" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="H24" s="209" t="s">
+      <c r="H24" s="180" t="s">
         <v>571</v>
       </c>
-      <c r="I24" s="185"/>
-      <c r="J24" s="186"/>
-      <c r="K24" s="184" t="s">
+      <c r="I24" s="181"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="212" t="s">
         <v>571</v>
       </c>
-      <c r="L24" s="185"/>
-      <c r="M24" s="185"/>
-      <c r="N24" s="186"/>
+      <c r="L24" s="181"/>
+      <c r="M24" s="181"/>
+      <c r="N24" s="182"/>
       <c r="O24" s="55" t="s">
         <v>477</v>
       </c>
@@ -32847,17 +32859,17 @@
       <c r="G25" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="H25" s="190" t="s">
+      <c r="H25" s="175" t="s">
         <v>571</v>
       </c>
-      <c r="I25" s="188"/>
-      <c r="J25" s="189"/>
-      <c r="K25" s="187" t="s">
+      <c r="I25" s="183"/>
+      <c r="J25" s="184"/>
+      <c r="K25" s="202" t="s">
         <v>571</v>
       </c>
-      <c r="L25" s="188"/>
-      <c r="M25" s="188"/>
-      <c r="N25" s="189"/>
+      <c r="L25" s="183"/>
+      <c r="M25" s="183"/>
+      <c r="N25" s="184"/>
       <c r="O25" s="52" t="s">
         <v>460</v>
       </c>
@@ -32884,17 +32896,17 @@
       <c r="G26" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="H26" s="190" t="s">
+      <c r="H26" s="175" t="s">
         <v>571</v>
       </c>
-      <c r="I26" s="188"/>
-      <c r="J26" s="189"/>
-      <c r="K26" s="187" t="s">
+      <c r="I26" s="183"/>
+      <c r="J26" s="184"/>
+      <c r="K26" s="202" t="s">
         <v>571</v>
       </c>
-      <c r="L26" s="188"/>
-      <c r="M26" s="188"/>
-      <c r="N26" s="189"/>
+      <c r="L26" s="183"/>
+      <c r="M26" s="183"/>
+      <c r="N26" s="184"/>
       <c r="O26" s="52" t="s">
         <v>460</v>
       </c>
@@ -32921,17 +32933,17 @@
       <c r="G27" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="H27" s="190" t="s">
+      <c r="H27" s="175" t="s">
         <v>571</v>
       </c>
-      <c r="I27" s="188"/>
-      <c r="J27" s="189"/>
-      <c r="K27" s="187" t="s">
+      <c r="I27" s="183"/>
+      <c r="J27" s="184"/>
+      <c r="K27" s="202" t="s">
         <v>571</v>
       </c>
-      <c r="L27" s="188"/>
-      <c r="M27" s="188"/>
-      <c r="N27" s="189"/>
+      <c r="L27" s="183"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="184"/>
       <c r="O27" s="52" t="s">
         <v>460</v>
       </c>
@@ -32958,17 +32970,17 @@
       <c r="G28" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="H28" s="190" t="s">
+      <c r="H28" s="175" t="s">
         <v>571</v>
       </c>
-      <c r="I28" s="188"/>
-      <c r="J28" s="189"/>
-      <c r="K28" s="187" t="s">
+      <c r="I28" s="183"/>
+      <c r="J28" s="184"/>
+      <c r="K28" s="202" t="s">
         <v>571</v>
       </c>
-      <c r="L28" s="188"/>
-      <c r="M28" s="188"/>
-      <c r="N28" s="189"/>
+      <c r="L28" s="183"/>
+      <c r="M28" s="183"/>
+      <c r="N28" s="184"/>
       <c r="O28" s="52" t="s">
         <v>460</v>
       </c>
@@ -32983,23 +32995,23 @@
       <c r="C29" s="61" t="s">
         <v>554</v>
       </c>
-      <c r="D29" s="169" t="s">
+      <c r="D29" s="172" t="s">
         <v>465</v>
       </c>
-      <c r="E29" s="169"/>
-      <c r="F29" s="169"/>
-      <c r="G29" s="190"/>
-      <c r="H29" s="190" t="s">
+      <c r="E29" s="172"/>
+      <c r="F29" s="172"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="175" t="s">
         <v>571</v>
       </c>
-      <c r="I29" s="188"/>
-      <c r="J29" s="189"/>
-      <c r="K29" s="187" t="s">
+      <c r="I29" s="183"/>
+      <c r="J29" s="184"/>
+      <c r="K29" s="202" t="s">
         <v>571</v>
       </c>
-      <c r="L29" s="188"/>
-      <c r="M29" s="188"/>
-      <c r="N29" s="189"/>
+      <c r="L29" s="183"/>
+      <c r="M29" s="183"/>
+      <c r="N29" s="184"/>
       <c r="O29" s="52" t="s">
         <v>460</v>
       </c>
@@ -33014,23 +33026,23 @@
       <c r="C30" s="61" t="s">
         <v>555</v>
       </c>
-      <c r="D30" s="169" t="s">
-        <v>465</v>
-      </c>
-      <c r="E30" s="169"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="190"/>
-      <c r="H30" s="190" t="s">
+      <c r="D30" s="172" t="s">
+        <v>750</v>
+      </c>
+      <c r="E30" s="172"/>
+      <c r="F30" s="172"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="175" t="s">
         <v>455</v>
       </c>
-      <c r="I30" s="188"/>
-      <c r="J30" s="189"/>
-      <c r="K30" s="187" t="s">
+      <c r="I30" s="183"/>
+      <c r="J30" s="184"/>
+      <c r="K30" s="202" t="s">
         <v>455</v>
       </c>
-      <c r="L30" s="188"/>
-      <c r="M30" s="188"/>
-      <c r="N30" s="189"/>
+      <c r="L30" s="183"/>
+      <c r="M30" s="183"/>
+      <c r="N30" s="184"/>
       <c r="O30" s="52" t="s">
         <v>460</v>
       </c>
@@ -33045,23 +33057,23 @@
       <c r="C31" s="61" t="s">
         <v>556</v>
       </c>
-      <c r="D31" s="169" t="s">
-        <v>465</v>
-      </c>
-      <c r="E31" s="169"/>
-      <c r="F31" s="169"/>
-      <c r="G31" s="190"/>
-      <c r="H31" s="190" t="s">
+      <c r="D31" s="172" t="s">
+        <v>750</v>
+      </c>
+      <c r="E31" s="172"/>
+      <c r="F31" s="172"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="175" t="s">
         <v>455</v>
       </c>
-      <c r="I31" s="188"/>
-      <c r="J31" s="189"/>
-      <c r="K31" s="187" t="s">
+      <c r="I31" s="183"/>
+      <c r="J31" s="184"/>
+      <c r="K31" s="202" t="s">
         <v>455</v>
       </c>
-      <c r="L31" s="188"/>
-      <c r="M31" s="188"/>
-      <c r="N31" s="189"/>
+      <c r="L31" s="183"/>
+      <c r="M31" s="183"/>
+      <c r="N31" s="184"/>
       <c r="O31" s="52" t="s">
         <v>460</v>
       </c>
@@ -33076,23 +33088,23 @@
       <c r="C32" s="60" t="s">
         <v>557</v>
       </c>
-      <c r="D32" s="195" t="s">
+      <c r="D32" s="200" t="s">
         <v>465</v>
       </c>
-      <c r="E32" s="195"/>
-      <c r="F32" s="195"/>
-      <c r="G32" s="196"/>
-      <c r="H32" s="182" t="s">
+      <c r="E32" s="200"/>
+      <c r="F32" s="200"/>
+      <c r="G32" s="201"/>
+      <c r="H32" s="193" t="s">
         <v>455</v>
       </c>
-      <c r="I32" s="171"/>
-      <c r="J32" s="172"/>
-      <c r="K32" s="170" t="s">
+      <c r="I32" s="194"/>
+      <c r="J32" s="195"/>
+      <c r="K32" s="203" t="s">
         <v>455</v>
       </c>
-      <c r="L32" s="171"/>
-      <c r="M32" s="171"/>
-      <c r="N32" s="172"/>
+      <c r="L32" s="194"/>
+      <c r="M32" s="194"/>
+      <c r="N32" s="195"/>
       <c r="O32" s="100" t="s">
         <v>446</v>
       </c>
@@ -33107,23 +33119,23 @@
       <c r="C33" s="60" t="s">
         <v>558</v>
       </c>
-      <c r="D33" s="195" t="s">
+      <c r="D33" s="200" t="s">
         <v>465</v>
       </c>
-      <c r="E33" s="195"/>
-      <c r="F33" s="195"/>
-      <c r="G33" s="196"/>
-      <c r="H33" s="182" t="s">
+      <c r="E33" s="200"/>
+      <c r="F33" s="200"/>
+      <c r="G33" s="201"/>
+      <c r="H33" s="193" t="s">
         <v>455</v>
       </c>
-      <c r="I33" s="171"/>
-      <c r="J33" s="172"/>
-      <c r="K33" s="170" t="s">
+      <c r="I33" s="194"/>
+      <c r="J33" s="195"/>
+      <c r="K33" s="203" t="s">
         <v>455</v>
       </c>
-      <c r="L33" s="171"/>
-      <c r="M33" s="171"/>
-      <c r="N33" s="172"/>
+      <c r="L33" s="194"/>
+      <c r="M33" s="194"/>
+      <c r="N33" s="195"/>
       <c r="O33" s="100" t="s">
         <v>446</v>
       </c>
@@ -33150,17 +33162,17 @@
       <c r="G34" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="H34" s="182" t="s">
+      <c r="H34" s="193" t="s">
         <v>571</v>
       </c>
-      <c r="I34" s="171"/>
-      <c r="J34" s="172"/>
-      <c r="K34" s="170" t="s">
+      <c r="I34" s="194"/>
+      <c r="J34" s="195"/>
+      <c r="K34" s="203" t="s">
         <v>571</v>
       </c>
-      <c r="L34" s="171"/>
-      <c r="M34" s="171"/>
-      <c r="N34" s="172"/>
+      <c r="L34" s="194"/>
+      <c r="M34" s="194"/>
+      <c r="N34" s="195"/>
       <c r="O34" s="100" t="s">
         <v>446</v>
       </c>
@@ -33187,17 +33199,17 @@
       <c r="G35" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="H35" s="182" t="s">
+      <c r="H35" s="193" t="s">
         <v>571</v>
       </c>
-      <c r="I35" s="171"/>
-      <c r="J35" s="172"/>
-      <c r="K35" s="170" t="s">
+      <c r="I35" s="194"/>
+      <c r="J35" s="195"/>
+      <c r="K35" s="203" t="s">
         <v>571</v>
       </c>
-      <c r="L35" s="171"/>
-      <c r="M35" s="171"/>
-      <c r="N35" s="172"/>
+      <c r="L35" s="194"/>
+      <c r="M35" s="194"/>
+      <c r="N35" s="195"/>
       <c r="O35" s="100" t="s">
         <v>446</v>
       </c>
@@ -33224,17 +33236,17 @@
       <c r="G36" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="H36" s="182" t="s">
+      <c r="H36" s="193" t="s">
         <v>571</v>
       </c>
-      <c r="I36" s="171"/>
-      <c r="J36" s="172"/>
-      <c r="K36" s="170" t="s">
+      <c r="I36" s="194"/>
+      <c r="J36" s="195"/>
+      <c r="K36" s="203" t="s">
         <v>571</v>
       </c>
-      <c r="L36" s="171"/>
-      <c r="M36" s="171"/>
-      <c r="N36" s="172"/>
+      <c r="L36" s="194"/>
+      <c r="M36" s="194"/>
+      <c r="N36" s="195"/>
       <c r="O36" s="100" t="s">
         <v>446</v>
       </c>
@@ -33261,17 +33273,17 @@
       <c r="G37" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="H37" s="183" t="s">
+      <c r="H37" s="211" t="s">
         <v>571</v>
       </c>
-      <c r="I37" s="174"/>
-      <c r="J37" s="175"/>
-      <c r="K37" s="173" t="s">
+      <c r="I37" s="205"/>
+      <c r="J37" s="206"/>
+      <c r="K37" s="204" t="s">
         <v>571</v>
       </c>
-      <c r="L37" s="174"/>
-      <c r="M37" s="174"/>
-      <c r="N37" s="175"/>
+      <c r="L37" s="205"/>
+      <c r="M37" s="205"/>
+      <c r="N37" s="206"/>
       <c r="O37" s="101" t="s">
         <v>446</v>
       </c>
@@ -33289,44 +33301,23 @@
         <v>443</v>
       </c>
     </row>
+    <row r="42" spans="2:16">
+      <c r="K42" s="38" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16">
+      <c r="K43" s="38" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16">
+      <c r="K44" s="38" t="s">
+        <v>753</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K34:N34"/>
-    <mergeCell ref="K35:N35"/>
     <mergeCell ref="K36:N36"/>
     <mergeCell ref="K37:N37"/>
     <mergeCell ref="C22:J22"/>
@@ -33343,6 +33334,42 @@
     <mergeCell ref="K28:N28"/>
     <mergeCell ref="K29:N29"/>
     <mergeCell ref="K30:N30"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="K35:N35"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -33366,44 +33393,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="B2" s="213" t="s">
+      <c r="B2" s="216" t="s">
         <v>616</v>
       </c>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="215" t="s">
         <v>615</v>
       </c>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="216" t="s">
         <v>373</v>
       </c>
-      <c r="E2" s="212" t="s">
+      <c r="E2" s="215" t="s">
         <v>608</v>
       </c>
-      <c r="F2" s="210"/>
-      <c r="G2" s="210" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="213" t="s">
         <v>631</v>
       </c>
-      <c r="H2" s="210" t="s">
+      <c r="H2" s="213" t="s">
         <v>730</v>
       </c>
       <c r="I2" s="114" t="s">
         <v>486</v>
       </c>
-      <c r="J2" s="212" t="s">
+      <c r="J2" s="215" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="213"/>
-      <c r="C3" s="212"/>
-      <c r="D3" s="213"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="211"/>
-      <c r="G3" s="211"/>
-      <c r="H3" s="211"/>
+      <c r="B3" s="216"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="216"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
       <c r="I3" s="115" t="s">
         <v>479</v>
       </c>
-      <c r="J3" s="212"/>
+      <c r="J3" s="215"/>
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="128" t="s">
@@ -34377,62 +34404,62 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="6" spans="3:3">
-      <c r="C6" s="214" t="s">
+      <c r="C6" s="164" t="s">
         <v>739</v>
       </c>
     </row>
     <row r="7" spans="3:3">
-      <c r="C7" s="215" t="s">
+      <c r="C7" s="165" t="s">
         <v>740</v>
       </c>
     </row>
     <row r="8" spans="3:3">
-      <c r="C8" s="215" t="s">
+      <c r="C8" s="165" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="9" spans="3:3">
-      <c r="C9" s="216" t="s">
+      <c r="C9" s="166" t="s">
         <v>742</v>
       </c>
     </row>
     <row r="10" spans="3:3">
-      <c r="C10" s="216" t="s">
+      <c r="C10" s="166" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="11" spans="3:3">
-      <c r="C11" s="216" t="s">
+      <c r="C11" s="166" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="12" spans="3:3">
-      <c r="C12" s="216" t="s">
+      <c r="C12" s="166" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="13" spans="3:3">
-      <c r="C13" s="216" t="s">
+      <c r="C13" s="166" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="14" spans="3:3">
-      <c r="C14" s="216" t="s">
+      <c r="C14" s="166" t="s">
         <v>746</v>
       </c>
     </row>
     <row r="15" spans="3:3">
-      <c r="C15" s="216" t="s">
+      <c r="C15" s="166" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="17" spans="3:3">
-      <c r="C17" s="214" t="s">
+      <c r="C17" s="164" t="s">
         <v>748</v>
       </c>
     </row>
     <row r="18" spans="3:3">
-      <c r="C18" s="215" t="s">
+      <c r="C18" s="165" t="s">
         <v>749</v>
       </c>
     </row>
@@ -35114,46 +35141,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="167" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
+      <c r="B1" s="167"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="167"/>
     </row>
     <row r="2" spans="1:22" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="164"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
+      <c r="A2" s="167"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="167"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="167"/>
+      <c r="F2" s="167"/>
     </row>
     <row r="3" spans="1:22" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
+      <c r="A3" s="167"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="167"/>
     </row>
     <row r="4" spans="1:22" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A4" s="164"/>
-      <c r="B4" s="164"/>
-      <c r="C4" s="164"/>
-      <c r="D4" s="164"/>
-      <c r="E4" s="164"/>
-      <c r="F4" s="164"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
     </row>
     <row r="5" spans="1:22" s="13" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A5" s="164"/>
-      <c r="B5" s="164"/>
-      <c r="C5" s="164"/>
-      <c r="D5" s="164"/>
-      <c r="E5" s="164"/>
-      <c r="F5" s="164"/>
+      <c r="A5" s="167"/>
+      <c r="B5" s="167"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
+      <c r="F5" s="167"/>
     </row>
     <row r="6" spans="1:22" ht="28.5" customHeight="1">
       <c r="A6" s="143" t="s">
